--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.1%</t>
+          <t>-186.0%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.842778671501486</v>
+        <v>3.842778671501483</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.808601802723148</v>
+        <v>-4.80844097084757</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8962495729823536</v>
+        <v>0.8963139057325846</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.367198601834567</v>
+        <v>-0.3670613669194141</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.59972755728462</v>
+        <v>2.599809898233712</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-642.4%</t>
+          <t>-632.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.6%</t>
+          <t>-282.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.3%</t>
+          <t>-149.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.7%</t>
+          <t>-251.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.0%</t>
+          <t>-180.7%</t>
         </is>
       </c>
     </row>
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.80844097084757</v>
+        <v>-4.70639826714777</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8963139057325846</v>
+        <v>0.9371309872125049</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3670613669194141</v>
+        <v>-0.2776423846395382</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.599809898233712</v>
+        <v>2.653461287601638</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-674.8%</t>
+          <t>-691.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.9%</t>
+          <t>449.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.2%</t>
+          <t>-672.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-270.3%</t>
+          <t>-277.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.5%</t>
+          <t>-298.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.2%</t>
+          <t>-147.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.8%</t>
+          <t>-260.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-186.1%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.9060596540435537</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.758548476395557</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-1.113625438435166</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.673346958758152</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.531379461982002</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.504172240844481</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.568392735755242</v>
+        <v>-1.734668931303805</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.489233147934107</v>
+        <v>2.422722669714682</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8954085957821715</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.776396794108319</v>
+        <v>-1.942672989656882</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.410923669146801</v>
+        <v>2.344413190927376</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8954085957821715</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.987809214996294</v>
+        <v>-2.154085410544858</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.3214401571296</v>
+        <v>2.254929678910174</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6839961748941964</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.326967592584817</v>
+        <v>-2.49324378813338</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.17886110540064</v>
+        <v>2.112350627181214</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3448377973056743</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.535458374036501</v>
+        <v>-2.701734569585065</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.115803082558734</v>
+        <v>2.049292604339309</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1363470158539899</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.782659558801723</v>
+        <v>-2.948935754350286</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.025021359061214</v>
+        <v>1.958510880841789</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1565003693528023</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.27504458682582</v>
+        <v>-3.441320782374383</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.829173739895307</v>
+        <v>1.762663261675882</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3358846586712944</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.660224977755892</v>
+        <v>-3.826501173304455</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.673644122336142</v>
+        <v>1.607133644116717</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3358846586712944</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.003907750982555</v>
+        <v>-4.170183946531118</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537940136500093</v>
+        <v>1.471429658280668</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4437907106985126</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.210419527869576</v>
+        <v>-4.376695723418139</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.451441484401542</v>
+        <v>1.384931006182117</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6503024875855341</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.466260613648269</v>
+        <v>-4.632536809196832</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.350877976790325</v>
+        <v>1.284367498570899</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6503024875855341</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.898066406798057</v>
+        <v>-5.06434260234662</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.164488546997814</v>
+        <v>1.097978068778389</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7867199840268011</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.132760400930609</v>
+        <v>-5.299036596479172</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.058895724346884</v>
+        <v>0.9923852461274585</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.7803837167975459</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.468423048161061</v>
+        <v>-5.634699243709624</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9232112571106676</v>
+        <v>0.8567007788912426</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.7803837167975459</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.832049293061375</v>
+        <v>-5.998325488609938</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7842483193847842</v>
+        <v>0.7177378411653588</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.8786053536646717</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.197176675700121</v>
+        <v>-6.363452871248684</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6374518813351169</v>
+        <v>0.5709414031156914</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.174916137963684</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.605765452880799</v>
+        <v>-6.772041648429363</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4727779144776045</v>
+        <v>0.4062674362581791</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.583504915144363</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.882341553196632</v>
+        <v>-7.048617748745196</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.357332906822732</v>
+        <v>0.2908224286033065</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.583504915144363</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.298733427483629</v>
+        <v>-7.465009623032193</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1887702077168107</v>
+        <v>0.1222597294973848</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.583504915144363</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.615345370024277</v>
+        <v>-7.781621565572841</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07238412136923023</v>
+        <v>0.005873643149804764</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.583504915144363</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.961220192009087</v>
+        <v>-8.127496387557651</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0698662422789984</v>
+        <v>-0.1363767204984239</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.583504915144363</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.124800070193471</v>
+        <v>-8.291076265742035</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1368932734977508</v>
+        <v>-0.2034037517171767</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.583504915144363</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.421461412003669</v>
+        <v>-8.587737607552233</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2517788342926219</v>
+        <v>-0.3182893125120478</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.652248050878241</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.626492592777986</v>
+        <v>-8.79276878832655</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3378176111367517</v>
+        <v>-0.4043280893561771</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.652248050878241</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.009493981520617</v>
+        <v>-9.175770177069181</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4911202679553881</v>
+        <v>-0.557630746174814</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.652248050878241</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.191363772505651</v>
+        <v>-9.357639968054215</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5612966683779721</v>
+        <v>-0.6278071465973976</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.834117841863276</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.550894095009653</v>
+        <v>-9.717170290558217</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6997584940815225</v>
+        <v>-0.7662689723009479</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.834117841863276</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.601243158463875</v>
+        <v>-9.767519354012439</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.711982099506034</v>
+        <v>-0.7784925777254594</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.884466905317498</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.698862435885271</v>
+        <v>-9.865138631433835</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7479880598528235</v>
+        <v>-0.8144985380722489</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.982086182738895</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.846388523890914</v>
+        <v>-10.01266471943948</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8041049387335084</v>
+        <v>-0.8706154169529339</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.129612270744539</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.05064669922078</v>
+        <v>-10.21692289476934</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8802950117468118</v>
+        <v>-0.9468054899662368</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.257251215358528</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.19245647342757</v>
+        <v>-10.35873266897613</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9325363669450906</v>
+        <v>-0.9990468451645165</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.428530013004103</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.11898664176012</v>
+        <v>-10.28526283730868</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8877767327846895</v>
+        <v>-0.9542872110041154</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.355060181336655</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.29411105914666</v>
+        <v>-10.46038725469522</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9432712789917908</v>
+        <v>-1.009781757211216</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.530184598723198</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.52856315316115</v>
+        <v>-10.69483934870971</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.044271281499182</v>
+        <v>-1.110781759718608</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.530184598723198</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.81636699769839</v>
+        <v>-10.98264319324695</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.166065010088054</v>
+        <v>-1.232575488307479</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.817988443260437</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.86915315329871</v>
+        <v>-11.03542934884728</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.186063682489628</v>
+        <v>-1.252574160709054</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.913663929842834</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.995189946667</v>
+        <v>-11.16146614221557</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.233784671207829</v>
+        <v>-1.300295149427255</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.888412307033091</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.94317443269819</v>
+        <v>-11.10945062824675</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.208988129933903</v>
+        <v>-1.275498608153328</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.888412307033091</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.08484627442231</v>
+        <v>-11.25112246997088</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.267132093522293</v>
+        <v>-1.333642571741718</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.888412307033091</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.03525542999748</v>
+        <v>-11.20153162554604</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.232242345587487</v>
+        <v>-1.298752823806912</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.838821462608257</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.83610332276038</v>
+        <v>-11.00237951830894</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.165632636339331</v>
+        <v>-1.232143114558756</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.673498936658444</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.61025817004097</v>
+        <v>-10.77653436558953</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.065715502215358</v>
+        <v>-1.132225980434783</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.63157226107128</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.48567951370338</v>
+        <v>-10.65195570925194</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.014744895124262</v>
+        <v>-1.081255373343687</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.63157226107128</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.53857480174766</v>
+        <v>-10.70485099729622</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.033269236179869</v>
+        <v>-1.099779714399294</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.626616914982834</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25466607081891</v>
+        <v>-10.42094226636748</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9139720395697326</v>
+        <v>-0.9804825177891576</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.626616914982834</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18329967820927</v>
+        <v>-10.34957587375783</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8951627449197392</v>
+        <v>-0.9616732231391643</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.555250522373186</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.919462811005197</v>
+        <v>-10.08573900655376</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7995114793510187</v>
+        <v>-0.8660219575704438</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.555250522373186</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.652221010136799</v>
+        <v>-9.818497205685361</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6944493195030335</v>
+        <v>-0.7609597977224585</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.555250522373186</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.554313971460308</v>
+        <v>-9.72059016700887</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6555868190058982</v>
+        <v>-0.7220972972253228</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.48726477251263</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.53036043048435</v>
+        <v>-9.696636626032912</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6453368964700212</v>
+        <v>-0.7118473746894463</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.463311231536672</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.266300492161553</v>
+        <v>-9.432576687710116</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5529732373026546</v>
+        <v>-0.6194837155220796</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.199251293213876</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.559220868656716</v>
+        <v>-8.725497064205278</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2729284215610206</v>
+        <v>-0.3394388997804456</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.199251293213876</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.519036570290526</v>
+        <v>-8.685312765839088</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2565110783267031</v>
+        <v>-0.3230215565461281</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.159066994847685</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.438966774752721</v>
+        <v>-8.605242970301283</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2251163388908246</v>
+        <v>-0.2916268171102492</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.078997199309881</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.205485552523122</v>
+        <v>-8.371761748071684</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1237994211611322</v>
+        <v>-0.1903098993805572</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.845515977080283</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.055819161515608</v>
+        <v>-8.22209535706417</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.06682507507108593</v>
+        <v>-0.1333355532905105</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.752612485837747</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.923543687884721</v>
+        <v>-8.089819883433282</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.01854739887170398</v>
+        <v>-0.08505787709112855</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.62033701220686</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.732944013211569</v>
+        <v>-7.89922020876013</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06050753168519352</v>
+        <v>-0.006002946534231057</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.429737337533707</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.483944214527988</v>
+        <v>-7.650220410076549</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1730137923822848</v>
+        <v>0.1065033141628602</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.429737337533707</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.589534204301092</v>
+        <v>-7.755810399849653</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.00280186687382411</v>
+        <v>-0.06370861134560002</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.535327327306812</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.608269106419689</v>
+        <v>-7.77454530196825</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04385224790347175</v>
+        <v>-0.02265823031595282</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.535327327306812</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.46032906501209</v>
+        <v>-7.626605260560651</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0168506582216561</v>
+        <v>-0.08336113644108067</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.515006411398254</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.443170914880795</v>
+        <v>-7.609447110429357</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01870138442261648</v>
+        <v>-0.08521186264204106</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.49784826126696</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.399622508110105</v>
+        <v>-7.565898703658666</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.008242633809433464</v>
+        <v>-0.07475311202885804</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.49784826126696</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.157474114656247</v>
+        <v>-7.323750310204808</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1030790779532529</v>
+        <v>0.03656859973382831</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.49784826126696</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.049214977533725</v>
+        <v>-7.215491173082286</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1409148532614566</v>
+        <v>0.07440437504203201</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.49784826126696</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.925923842716594</v>
+        <v>-7.092200038265156</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1877294011988857</v>
+        <v>0.1212189229794611</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.374557126449829</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.904774643813151</v>
+        <v>-7.071050839361712</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2038900589975885</v>
+        <v>0.1373795807781639</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.353407927546386</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.661009201829707</v>
+        <v>-6.959524485302929</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2971769441380165</v>
+        <v>0.1777708307487278</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.353407927546386</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.514112174111837</v>
+        <v>-6.812627457585059</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3580600691451807</v>
+        <v>0.238653955755892</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.305749685567798</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.264261780162762</v>
+        <v>-6.562777063635984</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4507423017085128</v>
+        <v>0.3313361883192241</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.305749685567798</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.08836968769533</v>
+        <v>-6.386884971168552</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.524698262216134</v>
+        <v>0.4052921488268453</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.305749685567798</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.916923224672867</v>
+        <v>-6.215438508146089</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6066043534796735</v>
+        <v>0.4871982400903847</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.134303222545335</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.691890225004044</v>
+        <v>-5.990405508477266</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6956380309634995</v>
+        <v>0.5762319175742108</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9092702228765118</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.628254482770109</v>
+        <v>-5.926769766243331</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7257871289113904</v>
+        <v>0.6063810155221017</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8456344806425773</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.535254441564211</v>
+        <v>-5.833769725037433</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7441814041775454</v>
+        <v>0.6247752907882567</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8456344806425773</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.294823944759351</v>
+        <v>-5.593339228232573</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8420966795243672</v>
+        <v>0.7226905661350784</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.605203983837717</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.222581376588156</v>
+        <v>-5.521096660061378</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8749230206276652</v>
+        <v>0.7555169072383765</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.605203983837717</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169583054306768</v>
+        <v>-5.46809833777999</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8968009334575604</v>
+        <v>0.7773948200682717</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5498677248357782</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.060778168827041</v>
+        <v>-5.359293452300263</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9373209588694444</v>
+        <v>0.8179148454801557</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5498677248357782</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.840757370790031</v>
+        <v>-5.139272654263253</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.026908315094863</v>
+        <v>0.9075022017055741</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4086478797677979</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.707889681726753</v>
+        <v>-5.006404965199975</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.095949573521997</v>
+        <v>0.9765434601327085</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4086478797677979</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.548374578207383</v>
+        <v>-4.846889861680605</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.160901459370047</v>
+        <v>1.041495345980758</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.249132776248428</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.403702433107646</v>
+        <v>-4.702217716580868</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.228858419971382</v>
+        <v>1.109452306582093</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1044606311486906</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.463577260465338</v>
+        <v>-4.76209254393856</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.190945980429731</v>
+        <v>1.071539867040442</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1643354585063827</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.376777762686329</v>
+        <v>-4.675293046159551</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.2480662728639</v>
+        <v>1.128660159474612</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1643354585063827</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.379247469148135</v>
+        <v>-4.677762752621357</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.24715079165259</v>
+        <v>1.127744678263302</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1668051649681889</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.447617655472145</v>
+        <v>-4.746132938945367</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.230809639597688</v>
+        <v>1.111403526208399</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1575294659319739</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.556155836388279</v>
+        <v>-4.854671119861501</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177831075863126</v>
+        <v>1.058424962473837</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1575294659319739</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.587148995716984</v>
+        <v>-4.885664279190206</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9901433771720307</v>
+        <v>0.870737263782742</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1575294659319739</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.411674735924516</v>
+        <v>-4.710190019397738</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064900313080806</v>
+        <v>0.9454941996915172</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1575294659319739</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.522610988565765</v>
+        <v>-4.821126272038986</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9962678407855134</v>
+        <v>0.8768617273962247</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1575294659319739</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.725637566108998</v>
+        <v>-5.02415284958222</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9181885949881257</v>
+        <v>0.7987824815988369</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3605560434752073</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.567711967173705</v>
+        <v>-4.866227250646927</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9915312209943752</v>
+        <v>0.8721251076050864</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3605560434752073</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.481468504147327</v>
+        <v>-4.779983787620549</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.020974876778787</v>
+        <v>0.901568763389498</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3605560434752073</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.526775323546307</v>
+        <v>-4.825290607019529</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9946279244637202</v>
+        <v>0.8752218110744314</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4013662064844381</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.555808428248608</v>
+        <v>-4.85432371172183</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9835665556159014</v>
+        <v>0.8641604422266127</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4013662064844381</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.462997946797748</v>
+        <v>-4.76151323027097</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9499634400876109</v>
+        <v>0.8305573266983222</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3085557250335788</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.507387416127176</v>
+        <v>-4.805902699600398</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9340811282804407</v>
+        <v>0.8146750148911519</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3529451943630064</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.394716197890926</v>
+        <v>-4.693231481364148</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9742253240866638</v>
+        <v>0.8548192106973751</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2402739761267562</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.282339196708253</v>
+        <v>-4.580854480181475</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.0246674203904</v>
+        <v>0.9052613070011115</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2402739761267562</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.480573765594984</v>
+        <v>-4.779089049068205</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.956870794604247</v>
+        <v>0.8374646812149582</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4385085450134868</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.563575046620262</v>
+        <v>-4.862090330093484</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7620260021947887</v>
+        <v>0.6426198888054999</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4570794295406606</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.690642052927251</v>
+        <v>-4.989157336400472</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8313488603911989</v>
+        <v>0.7119427470019102</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4570794295406606</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.777240635908353</v>
+        <v>-5.075755919381575</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8112224533010808</v>
+        <v>0.6918163399117923</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4570794295406606</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.738856973350202</v>
+        <v>-5.037372256823424</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.82399535966671</v>
+        <v>0.704589246277421</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.4186957669825094</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.561740643315036</v>
+        <v>-4.860255926788258</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8915709205260782</v>
+        <v>0.7721648071367895</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.4186957669825094</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.532038519338743</v>
+        <v>-4.830553802811965</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.904135161878509</v>
+        <v>0.7847290484892202</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4231658921978227</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.352663098099975</v>
+        <v>-4.651178381573197</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9696723056804304</v>
+        <v>0.8502661922911416</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.2663891340271041</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.397677311620582</v>
+        <v>-4.696192595093803</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9324740756037775</v>
+        <v>0.8130679622144887</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.2967380293417087</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.664681821893017</v>
+        <v>-4.963197105366238</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8313638338337492</v>
+        <v>0.7119577204444605</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.4911010673846573</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.765879603330189</v>
+        <v>-5.064394886803411</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7900886431553815</v>
+        <v>0.6706825297660926</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.5595098809299764</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.733404017159417</v>
+        <v>-5.031919300632639</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8006788391780071</v>
+        <v>0.6812727257887183</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.5595098809299764</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.71436588945212</v>
+        <v>-5.012881172925342</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8048188094691708</v>
+        <v>0.6854126960798821</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.617693492261171</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.745492520602738</v>
+        <v>-5.04400780407596</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9699500259476042</v>
+        <v>0.8505439125583152</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.617693492261171</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.79781290120353</v>
+        <v>-5.096328184676752</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9498552026934211</v>
+        <v>0.8304490893041323</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5827466322522988</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.942135807128449</v>
+        <v>-5.240651090601671</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8981345707203794</v>
+        <v>0.7787284573310904</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5827466322522988</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.794392836893446</v>
+        <v>-5.092908120366668</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.036384406606402</v>
+        <v>0.9169782932171135</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.4149392750174157</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.896407519424668</v>
+        <v>-5.19492280289789</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9983721551253948</v>
+        <v>0.8789660417361058</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.4149392750174157</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.759798175330575</v>
+        <v>-5.058313458803797</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05367824115469</v>
+        <v>0.9342721277654014</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2783299309233232</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.902563508153225</v>
+        <v>-5.201078791626447</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9956525847657405</v>
+        <v>0.8762464713764517</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.4210952637459736</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.840265509377103</v>
+        <v>-5.138780792850325</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.08690733807301</v>
+        <v>0.9675012246837214</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.4210952637459736</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.638475311711945</v>
+        <v>-4.936990595185167</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8762042895284714</v>
+        <v>0.7567981761391827</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.2230770715768192</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.578584630069352</v>
+        <v>-4.877099913542573</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9704507945076839</v>
+        <v>0.8510446811183952</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.1631863899342257</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.676325174694326</v>
+        <v>-4.974840458167548</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9459823127737379</v>
+        <v>0.8265761993844492</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1790756680672059</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.852662934817255</v>
+        <v>-5.151178218290477</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8739831895492378</v>
+        <v>0.7545770761599488</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.3554134281901353</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.851973562656032</v>
+        <v>-5.150488846129254</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8727505564536555</v>
+        <v>0.7533444430643668</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.3554134281901353</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.858544527710625</v>
+        <v>-5.157059811183847</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8699850378672547</v>
+        <v>0.7505789244779661</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.3619843932447283</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.850590557415853</v>
+        <v>-5.149105840889074</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8731666259851636</v>
+        <v>0.7537605125958748</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.3619843932447283</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.840217181082766</v>
+        <v>-5.138732464555988</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8836977335462031</v>
+        <v>0.7642916201569143</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.351611016911641</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.712532871288469</v>
+        <v>-5.011048154761691</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9396638308386462</v>
+        <v>0.8202577174493575</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.2239267071173445</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.773199461690858</v>
+        <v>-5.07171474516408</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9021518671535631</v>
+        <v>0.7827457537642744</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3056250238358782</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.708205601757212</v>
+        <v>-5.006720885230434</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9322471137376498</v>
+        <v>0.812841000348361</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.2787944092317228</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.842778671501483</v>
+        <v>3.580782676799547</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.70639826714777</v>
+        <v>-5.107479520987432</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9371309872125049</v>
+        <v>0.7766984856766399</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2776423846395382</v>
+        <v>-0.3676199779587283</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.653461287601638</v>
+        <v>2.599474731610123</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-41.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-691.5%</t>
+          <t>-691.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.5%</t>
+          <t>449.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.3%</t>
+          <t>-659.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.6%</t>
+          <t>-293.2%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.1%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1982"/>
+  <dimension ref="A1:G1983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9060596540435537</v>
+        <v>-0.9055146351874247</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.758548476395557</v>
+        <v>2.758766483938009</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.113625438435166</v>
+        <v>-1.113080419579037</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.673346958758152</v>
+        <v>2.673564966300604</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.531379461982002</v>
+        <v>-1.530834443125874</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.504172240844481</v>
+        <v>2.504390248386933</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.734668931303805</v>
+        <v>-1.734123912447676</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.422722669714682</v>
+        <v>2.422940677257134</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8954085957821715</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.942672989656882</v>
+        <v>-1.942127970800754</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.344413190927376</v>
+        <v>2.344631198469828</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8954085957821715</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.154085410544858</v>
+        <v>-2.153540391688729</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.254929678910174</v>
+        <v>2.255147686452626</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6839961748941964</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.49324378813338</v>
+        <v>-2.492698769277251</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.112350627181214</v>
+        <v>2.112568634723666</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3448377973056743</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.701734569585065</v>
+        <v>-2.701189550728936</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.049292604339309</v>
+        <v>2.04951061188176</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1363470158539899</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.948935754350286</v>
+        <v>-2.948390735494157</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.958510880841789</v>
+        <v>1.958728888384241</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1565003693528023</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.441320782374383</v>
+        <v>-3.440775763518254</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.762663261675882</v>
+        <v>1.762881269218334</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3358846586712944</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.826501173304455</v>
+        <v>-3.825956154448326</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.607133644116717</v>
+        <v>1.607351651659168</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3358846586712944</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.170183946531118</v>
+        <v>-4.169638927674989</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.471429658280668</v>
+        <v>1.471647665823119</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4437907106985126</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.376695723418139</v>
+        <v>-4.37615070456201</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.384931006182117</v>
+        <v>1.385149013724568</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6503024875855341</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.632536809196832</v>
+        <v>-4.631991790340703</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.284367498570899</v>
+        <v>1.284585506113351</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6503024875855341</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.06434260234662</v>
+        <v>-5.063797583490491</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.097978068778389</v>
+        <v>1.09819607632084</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7867199840268011</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.299036596479172</v>
+        <v>-5.298491577623043</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9923852461274585</v>
+        <v>0.9926032536699099</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.7803837167975459</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.634699243709624</v>
+        <v>-5.634154224853495</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8567007788912426</v>
+        <v>0.856918786433694</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.7803837167975459</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.998325488609938</v>
+        <v>-5.997780469753809</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7177378411653588</v>
+        <v>0.7179558487078106</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.8786053536646717</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.363452871248684</v>
+        <v>-6.362907852392556</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5709414031156914</v>
+        <v>0.5711594106581432</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.174916137963684</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.772041648429363</v>
+        <v>-6.771496629573234</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4062674362581791</v>
+        <v>0.4064854438006309</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.583504915144363</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.048617748745196</v>
+        <v>-7.048072729889066</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2908224286033065</v>
+        <v>0.2910404361457584</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.583504915144363</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.465009623032193</v>
+        <v>-7.464464604176063</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1222597294973848</v>
+        <v>0.1224777370398371</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.583504915144363</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.781621565572841</v>
+        <v>-7.781076546716712</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.005873643149804764</v>
+        <v>0.006091650692256589</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.583504915144363</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.127496387557651</v>
+        <v>-8.126951368701521</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1363767204984239</v>
+        <v>-0.136158712955972</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.583504915144363</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.291076265742035</v>
+        <v>-8.290531246885905</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2034037517171767</v>
+        <v>-0.2031857441747245</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.583504915144363</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.587737607552233</v>
+        <v>-8.587192588696103</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3182893125120478</v>
+        <v>-0.3180713049695956</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.652248050878241</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.79276878832655</v>
+        <v>-8.79222376947042</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4043280893561771</v>
+        <v>-0.4041100818137253</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.652248050878241</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.175770177069181</v>
+        <v>-9.175225158213051</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.557630746174814</v>
+        <v>-0.5574127386323617</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.652248050878241</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.357639968054215</v>
+        <v>-9.357094949198085</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6278071465973976</v>
+        <v>-0.6275891390549457</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.834117841863276</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.717170290558217</v>
+        <v>-9.716625271702087</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7662689723009479</v>
+        <v>-0.7660509647584961</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.834117841863276</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.767519354012439</v>
+        <v>-9.766974335156309</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7784925777254594</v>
+        <v>-0.7782745701830076</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.884466905317498</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.865138631433835</v>
+        <v>-9.864593612577705</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8144985380722489</v>
+        <v>-0.8142805305297971</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.982086182738895</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.01266471943948</v>
+        <v>-10.01211970058335</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8706154169529339</v>
+        <v>-0.8703974094104816</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.129612270744539</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.21692289476934</v>
+        <v>-10.21637787591321</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9468054899662368</v>
+        <v>-0.9465874824237854</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.257251215358528</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.35873266897613</v>
+        <v>-10.35818765012</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9990468451645165</v>
+        <v>-0.9988288376220642</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.428530013004103</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.28526283730868</v>
+        <v>-10.28471781845255</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9542872110041154</v>
+        <v>-0.9540692034616631</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.355060181336655</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.46038725469522</v>
+        <v>-10.45984223583909</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.009781757211216</v>
+        <v>-1.009563749668764</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.530184598723198</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.69483934870971</v>
+        <v>-10.69429432985358</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.110781759718608</v>
+        <v>-1.110563752176156</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.530184598723198</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.98264319324695</v>
+        <v>-10.98209817439082</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.232575488307479</v>
+        <v>-1.232357480765028</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.817988443260437</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.03542934884728</v>
+        <v>-11.03488432999115</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.252574160709054</v>
+        <v>-1.252356153166602</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.913663929842834</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.16146614221557</v>
+        <v>-11.16092112335944</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.300295149427255</v>
+        <v>-1.300077141884803</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.888412307033091</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.10945062824675</v>
+        <v>-11.10890560939063</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.275498608153328</v>
+        <v>-1.275280600610877</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.888412307033091</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.25112246997088</v>
+        <v>-11.25057745111475</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.333642571741718</v>
+        <v>-1.333424564199267</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.888412307033091</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.20153162554604</v>
+        <v>-11.20098660668991</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.298752823806912</v>
+        <v>-1.298534816264461</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.838821462608257</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.00237951830894</v>
+        <v>-11.00183449945281</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.232143114558756</v>
+        <v>-1.231925107016304</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.673498936658444</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.77653436558953</v>
+        <v>-10.7759893467334</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.132225980434783</v>
+        <v>-1.13200797289233</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.63157226107128</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.65195570925194</v>
+        <v>-10.65141069039581</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.081255373343687</v>
+        <v>-1.081037365801235</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.63157226107128</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.70485099729622</v>
+        <v>-10.70430597844009</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.099779714399294</v>
+        <v>-1.099561706856842</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.626616914982834</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42094226636748</v>
+        <v>-10.42039724751135</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9804825177891576</v>
+        <v>-0.9802645102467062</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.626616914982834</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34957587375783</v>
+        <v>-10.3490308549017</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9616732231391643</v>
+        <v>-0.961455215596712</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.555250522373186</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08573900655376</v>
+        <v>-10.08519398769763</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8660219575704438</v>
+        <v>-0.8658039500279915</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.555250522373186</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.818497205685361</v>
+        <v>-9.817952186829231</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7609597977224585</v>
+        <v>-0.7607417901800066</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.555250522373186</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.72059016700887</v>
+        <v>-9.720045148152741</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7220972972253228</v>
+        <v>-0.721879289682871</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.48726477251263</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.696636626032912</v>
+        <v>-9.696091607176783</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7118473746894463</v>
+        <v>-0.7116293671469944</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.463311231536672</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.432576687710116</v>
+        <v>-9.432031668853986</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6194837155220796</v>
+        <v>-0.6192657079796278</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.199251293213876</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.725497064205278</v>
+        <v>-8.724952045349148</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3394388997804456</v>
+        <v>-0.3392208922379938</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.199251293213876</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.685312765839088</v>
+        <v>-8.684767746982958</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3230215565461281</v>
+        <v>-0.3228035490036762</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.159066994847685</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.605242970301283</v>
+        <v>-8.604697951445154</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2916268171102492</v>
+        <v>-0.2914088095677974</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.078997199309881</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.371761748071684</v>
+        <v>-8.371216729215554</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1903098993805572</v>
+        <v>-0.1900918918381054</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.845515977080283</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.22209535706417</v>
+        <v>-8.22155033820804</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1333355532905105</v>
+        <v>-0.1331175457480587</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.752612485837747</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.089819883433282</v>
+        <v>-8.089274864577153</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08505787709112855</v>
+        <v>-0.08483986954867673</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.62033701220686</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.89922020876013</v>
+        <v>-7.898675189904</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.006002946534231057</v>
+        <v>-0.005784938991778787</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.429737337533707</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.650220410076549</v>
+        <v>-7.649675391220419</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1065033141628602</v>
+        <v>0.106721321705312</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.429737337533707</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.755810399849653</v>
+        <v>-7.755265380993523</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06370861134560002</v>
+        <v>-0.06349060380314819</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.535327327306812</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.77454530196825</v>
+        <v>-7.77400028311212</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02265823031595282</v>
+        <v>-0.02244022277350055</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.535327327306812</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.626605260560651</v>
+        <v>-7.626060241704521</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08336113644108067</v>
+        <v>-0.0831431288986284</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.515006411398254</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.609447110429357</v>
+        <v>-7.608902091573227</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08521186264204106</v>
+        <v>-0.08499385509958923</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.49784826126696</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.565898703658666</v>
+        <v>-7.565353684802536</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07475311202885804</v>
+        <v>-0.07453510448640621</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.49784826126696</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.323750310204808</v>
+        <v>-7.323205291348678</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03656859973382831</v>
+        <v>0.03678660727628014</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.49784826126696</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.215491173082286</v>
+        <v>-7.214946154226157</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07440437504203201</v>
+        <v>0.07462238258448384</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.49784826126696</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.092200038265156</v>
+        <v>-7.091655019409026</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1212189229794611</v>
+        <v>0.1214369305219134</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.374557126449829</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.071050839361712</v>
+        <v>-7.070505820505582</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1373795807781639</v>
+        <v>0.1375975883206157</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.353407927546386</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.959524485302929</v>
+        <v>-6.826740378522138</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1777708307487278</v>
+        <v>0.2308844734610442</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.353407927546386</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.812627457585059</v>
+        <v>-6.679843350804267</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.238653955755892</v>
+        <v>0.2917675984682084</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.305749685567798</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.562777063635984</v>
+        <v>-6.429992956855193</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3313361883192241</v>
+        <v>0.3844498310315405</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.305749685567798</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.386884971168552</v>
+        <v>-6.254100864387761</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4052921488268453</v>
+        <v>0.4584057915391622</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.305749685567798</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.215438508146089</v>
+        <v>-6.082654401365297</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4871982400903847</v>
+        <v>0.5403118828027011</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.134303222545335</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.990405508477266</v>
+        <v>-5.857621401696474</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5762319175742108</v>
+        <v>0.6293455602865272</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9092702228765118</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.926769766243331</v>
+        <v>-5.79398565946254</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6063810155221017</v>
+        <v>0.6594946582344186</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8456344806425773</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.833769725037433</v>
+        <v>-5.700985618256642</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6247752907882567</v>
+        <v>0.6778889335005731</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8456344806425773</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.593339228232573</v>
+        <v>-5.460555121451781</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7226905661350784</v>
+        <v>0.7758042088473949</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.605203983837717</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.521096660061378</v>
+        <v>-5.388312553280587</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7555169072383765</v>
+        <v>0.8086305499506929</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.605203983837717</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.46809833777999</v>
+        <v>-5.335314230999199</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7773948200682717</v>
+        <v>0.8305084627805881</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5498677248357782</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.359293452300263</v>
+        <v>-5.226509345519472</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8179148454801557</v>
+        <v>0.8710284881924721</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5498677248357782</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.139272654263253</v>
+        <v>-5.006488547482461</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9075022017055741</v>
+        <v>0.9606158444178907</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4086478797677979</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.006404965199975</v>
+        <v>-4.873620858419184</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9765434601327085</v>
+        <v>1.029657102845025</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4086478797677979</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.846889861680605</v>
+        <v>-4.714105754899814</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.041495345980758</v>
+        <v>1.094608988693075</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.249132776248428</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.702217716580868</v>
+        <v>-4.569433609800076</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.109452306582093</v>
+        <v>1.16256594929441</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1044606311486906</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.76209254393856</v>
+        <v>-4.629308437157769</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.071539867040442</v>
+        <v>1.124653509752759</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1643354585063827</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.675293046159551</v>
+        <v>-4.542508939378759</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.128660159474612</v>
+        <v>1.181773802186928</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1643354585063827</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.677762752621357</v>
+        <v>-4.544978645840565</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.127744678263302</v>
+        <v>1.180858320975618</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1668051649681889</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.746132938945367</v>
+        <v>-4.613348832164576</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.111403526208399</v>
+        <v>1.164517168920716</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1575294659319739</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.854671119861501</v>
+        <v>-4.72188701308071</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.058424962473837</v>
+        <v>1.111538605186154</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1575294659319739</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.885664279190206</v>
+        <v>-4.752880172409415</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.870737263782742</v>
+        <v>0.9238509064950584</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1575294659319739</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.710190019397738</v>
+        <v>-4.577405912616946</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9454941996915172</v>
+        <v>0.9986078424038336</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1575294659319739</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.821126272038986</v>
+        <v>-4.688342165258195</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8768617273962247</v>
+        <v>0.9299753701085411</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1575294659319739</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.02415284958222</v>
+        <v>-4.891368742801428</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7987824815988369</v>
+        <v>0.8518961243111534</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3605560434752073</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.866227250646927</v>
+        <v>-4.733443143866135</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8721251076050864</v>
+        <v>0.9252387503174031</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3605560434752073</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.779983787620549</v>
+        <v>-4.647199680839758</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.901568763389498</v>
+        <v>0.9546824061018144</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3605560434752073</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.825290607019529</v>
+        <v>-4.692506500238737</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8752218110744314</v>
+        <v>0.9283354537867481</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4013662064844381</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.85432371172183</v>
+        <v>-4.721539604941039</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8641604422266127</v>
+        <v>0.9172740849389291</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4013662064844381</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.76151323027097</v>
+        <v>-4.628729123490179</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8305573266983222</v>
+        <v>0.8836709694106386</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3085557250335788</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.805902699600398</v>
+        <v>-4.673118592819606</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8146750148911519</v>
+        <v>0.8677886576034686</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3529451943630064</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.693231481364148</v>
+        <v>-4.560447374583356</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8548192106973751</v>
+        <v>0.9079328534096915</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2402739761267562</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.580854480181475</v>
+        <v>-4.448070373400683</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9052613070011115</v>
+        <v>0.958374949713428</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2402739761267562</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.779089049068205</v>
+        <v>-4.646304942287414</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8374646812149582</v>
+        <v>0.8905783239272747</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.4385085450134868</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.862090330093484</v>
+        <v>-4.729306223312693</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6426198888054999</v>
+        <v>0.6957335315178164</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.4570794295406606</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.989157336400472</v>
+        <v>-4.856373229619681</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7119427470019102</v>
+        <v>0.7650563897142268</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.4570794295406606</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.075755919381575</v>
+        <v>-4.942971812600784</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6918163399117923</v>
+        <v>0.7449299826241087</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.4570794295406606</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.037372256823424</v>
+        <v>-4.904588150042633</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.704589246277421</v>
+        <v>0.7577028889897377</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.4186957669825094</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.860255926788258</v>
+        <v>-4.727471820007467</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7721648071367895</v>
+        <v>0.8252784498491061</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.4186957669825094</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.830553802811965</v>
+        <v>-4.697769696031173</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7847290484892202</v>
+        <v>0.8378426912015366</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.4231658921978227</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.651178381573197</v>
+        <v>-4.518394274792406</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8502661922911416</v>
+        <v>0.9033798350034581</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.2663891340271041</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.696192595093803</v>
+        <v>-4.563408488313012</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8130679622144887</v>
+        <v>0.8661816049268052</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.2967380293417087</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.963197105366238</v>
+        <v>-4.830412998585447</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7119577204444605</v>
+        <v>0.7650713631567769</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.4911010673846573</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.064394886803411</v>
+        <v>-4.93161078002262</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6706825297660926</v>
+        <v>0.7237961724784092</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.5595098809299764</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.031919300632639</v>
+        <v>-4.899135193851848</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6812727257887183</v>
+        <v>0.7343863685010348</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.5595098809299764</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.012881172925342</v>
+        <v>-4.88009706614455</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6854126960798821</v>
+        <v>0.7385263387921988</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.617693492261171</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.04400780407596</v>
+        <v>-4.911223697295169</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8505439125583152</v>
+        <v>0.9036575552706319</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.617693492261171</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.096328184676752</v>
+        <v>-4.963544077895961</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8304490893041323</v>
+        <v>0.8835627320164487</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5827466322522988</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.240651090601671</v>
+        <v>-5.107866983820879</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7787284573310904</v>
+        <v>0.8318421000434073</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5827466322522988</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.092908120366668</v>
+        <v>-4.960124013585877</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9169782932171135</v>
+        <v>0.97009193592943</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.4149392750174157</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.19492280289789</v>
+        <v>-5.062138696117098</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8789660417361058</v>
+        <v>0.9320796844484227</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.4149392750174157</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.058313458803797</v>
+        <v>-4.925529352023005</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9342721277654014</v>
+        <v>0.987385770477718</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2783299309233232</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.201078791626447</v>
+        <v>-5.068294684845656</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8762464713764517</v>
+        <v>0.9293601140887682</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.4210952637459736</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.138780792850325</v>
+        <v>-5.005996686069533</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9675012246837214</v>
+        <v>1.020614867396038</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.4210952637459736</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.936990595185167</v>
+        <v>-4.804206488404375</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7567981761391827</v>
+        <v>0.8099118188514991</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.2230770715768192</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.877099913542573</v>
+        <v>-4.744315806761782</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8510446811183952</v>
+        <v>0.9041583238307118</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.1631863899342257</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.974840458167548</v>
+        <v>-4.842056351386756</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8265761993844492</v>
+        <v>0.8796898420967656</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.1790756680672059</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.151178218290477</v>
+        <v>-5.018394111509686</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7545770761599488</v>
+        <v>0.8076907188722657</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.3554134281901353</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.150488846129254</v>
+        <v>-5.017704739348463</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7533444430643668</v>
+        <v>0.8064580857766832</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.3554134281901353</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.157059811183847</v>
+        <v>-5.024275704403055</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7505789244779661</v>
+        <v>0.8036925671902826</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.3619843932447283</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.149105840889074</v>
+        <v>-5.016321734108283</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7537605125958748</v>
+        <v>0.8068741553081913</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.3619843932447283</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.138732464555988</v>
+        <v>-5.005948357775196</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7642916201569143</v>
+        <v>0.8174052628692308</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.351611016911641</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.011048154761691</v>
+        <v>-4.8782640479809</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8202577174493575</v>
+        <v>0.8733713601616742</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.2239267071173445</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.07171474516408</v>
+        <v>-4.938930638383288</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7827457537642744</v>
+        <v>0.8358593964765908</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.3056250238358782</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.006720885230434</v>
+        <v>-4.873936778449643</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.812841000348361</v>
+        <v>0.8659546430606777</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.2787944092317228</v>
@@ -47131,22 +47131,45 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.580782676799547</v>
+        <v>3.817961388674306</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.107479520987432</v>
+        <v>-4.974695414206641</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7766984856766399</v>
+        <v>0.8298121283889563</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.3676199779587283</v>
       </c>
       <c r="G1982" t="n">
         <v>2.599474731610123</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="2" t="n">
+        <v>45445</v>
+      </c>
+      <c r="B1983" t="n">
+        <v>3.581042179381065</v>
+      </c>
+      <c r="C1983" t="n">
+        <v>2.704115520070538</v>
+      </c>
+      <c r="D1983" t="n">
+        <v>-4.974695414206641</v>
+      </c>
+      <c r="E1983" t="n">
+        <v>0.8298121283889563</v>
+      </c>
+      <c r="F1983" t="n">
+        <v>-0.3676199779587283</v>
+      </c>
+      <c r="G1983" t="n">
+        <v>2.697179317056905</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.78434395226416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674306</v>
+        <v>3.817961388674305</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.581042179381065</v>
+        <v>3.581042179381063</v>
       </c>
       <c r="C1983" t="n">
         <v>2.704115520070538</v>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-33.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-691.4%</t>
+          <t>-678.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.6%</t>
+          <t>454.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.0%</t>
+          <t>-662.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.0%</t>
+          <t>-271.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>169.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-293.2%</t>
+          <t>-283.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-302.0%</t>
+          <t>-305.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-151.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.8%</t>
+          <t>-264.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-181.6%</t>
+          <t>-183.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-168.8%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9055146351874247</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.758766483938009</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.113080419579037</v>
+        <v>-0.9830893725955661</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.673564966300604</v>
+        <v>2.725561385093993</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.275083208563437</v>
+        <v>1.239343078854473</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.884203483584028</v>
+        <v>3.86275940575865</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.530834443125874</v>
+        <v>-1.400843396142403</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.504390248386933</v>
+        <v>2.556386667180321</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8573291850165997</v>
+        <v>0.8215890553076358</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.631477960960989</v>
+        <v>3.610033883135611</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.734123912447676</v>
+        <v>-1.604132865464206</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.422940677257134</v>
+        <v>2.474937096050521</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8954085957821715</v>
+        <v>0.8596684660732076</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.654191824019255</v>
+        <v>3.632747746193876</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.942127970800754</v>
+        <v>-1.812136923817283</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.344631198469828</v>
+        <v>2.396627617263216</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8954085957821715</v>
+        <v>0.8596684660732076</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.65908396857318</v>
+        <v>3.637639890747801</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.153540391688729</v>
+        <v>-2.023549344705258</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.255147686452626</v>
+        <v>2.307144105246014</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6839961748941964</v>
+        <v>0.6482560451852325</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.527317972378383</v>
+        <v>3.505873894553004</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.492698769277251</v>
+        <v>-2.36270772229378</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.112568634723666</v>
+        <v>2.164565053517054</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3448377973056743</v>
+        <v>0.3090976675967104</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.316907245131719</v>
+        <v>3.29546316730634</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.701189550728936</v>
+        <v>-2.571198503745465</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.04951061188176</v>
+        <v>2.101507030675148</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1363470158539899</v>
+        <v>0.100606886145026</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.212151065999476</v>
+        <v>3.190706988174098</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.948390735494157</v>
+        <v>-2.818399688510686</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.958728888384241</v>
+        <v>2.010725307177629</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1565003693528023</v>
+        <v>0.1207602396438384</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.232341828507332</v>
+        <v>3.210897750681954</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.440775763518254</v>
+        <v>-3.310784716534783</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.762881269218334</v>
+        <v>1.814877688011722</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3358846586712944</v>
+        <v>-0.3716247883802583</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.938017203736606</v>
+        <v>2.916573125911228</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.825956154448326</v>
+        <v>-3.695965107464855</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.607351651659168</v>
+        <v>1.659348070452557</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3358846586712944</v>
+        <v>-0.3716247883802583</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.936559742549469</v>
+        <v>2.915115664724091</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.169638927674989</v>
+        <v>-4.039647880691518</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.471647665823119</v>
+        <v>1.523644084616508</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4437907106985126</v>
+        <v>-0.4795308404074765</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.873585234787755</v>
+        <v>2.852141156962376</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.37615070456201</v>
+        <v>-4.24615965757854</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.385149013724568</v>
+        <v>1.437145432517957</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6503024875855341</v>
+        <v>-0.686042617294498</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.7457842273118</v>
+        <v>2.724340149486421</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.631991790340703</v>
+        <v>-4.502000743357232</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.284585506113351</v>
+        <v>1.336581924906739</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6503024875855341</v>
+        <v>-0.686042617294498</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.747557154012059</v>
+        <v>2.726113076186681</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.063797583490491</v>
+        <v>-4.93380653650702</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.09819607632084</v>
+        <v>1.150192495114229</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7867199840268011</v>
+        <v>-0.822460113735765</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.652039543614704</v>
+        <v>2.630595465789325</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.298491577623043</v>
+        <v>-5.168500530639572</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9926032536699099</v>
+        <v>1.044599672463298</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7803837167975459</v>
+        <v>-0.8161238465065098</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.644126078954347</v>
+        <v>2.622682001128969</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.634154224853495</v>
+        <v>-5.504163177870025</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.856918786433694</v>
+        <v>0.9089152052270824</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7803837167975459</v>
+        <v>-0.8161238465065098</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.642706670610313</v>
+        <v>2.621262592784934</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.997780469753809</v>
+        <v>-5.867789422770338</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7179558487078106</v>
+        <v>0.7699522675011989</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8786053536646717</v>
+        <v>-0.9143454833736356</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.590261248724278</v>
+        <v>2.5688171708989</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.362907852392556</v>
+        <v>-6.232916805409085</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5711594106581432</v>
+        <v>0.6231558294515316</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.174916137963684</v>
+        <v>-1.210656267672648</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.411729293150702</v>
+        <v>2.390285215325324</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.771496629573234</v>
+        <v>-6.641505582589764</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4064854438006309</v>
+        <v>0.4584818625940188</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.165337570857054</v>
+        <v>2.143893493031676</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.048072729889066</v>
+        <v>-6.918081682905596</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2910404361457584</v>
+        <v>0.3430368549391467</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.160523003328515</v>
+        <v>2.139078925503137</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.464464604176063</v>
+        <v>-7.334473557192593</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1224777370398371</v>
+        <v>0.174474155833225</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.158517053937392</v>
+        <v>2.137072976112014</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.781076546716712</v>
+        <v>-7.651085499733242</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.006091650692256589</v>
+        <v>0.05808806948564449</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.168775744606071</v>
+        <v>2.147331666780693</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.126951368701521</v>
+        <v>-7.996960321718051</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.136158712955972</v>
+        <v>-0.0841622941625837</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.164875309751767</v>
+        <v>2.143431231926388</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.290531246885905</v>
+        <v>-8.160540199902435</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2031857441747245</v>
+        <v>-0.1511893253813366</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.619245044853327</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.163280229806768</v>
+        <v>2.141836151981389</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.587192588696103</v>
+        <v>-8.457201541712633</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3180713049695956</v>
+        <v>-0.2660748861762077</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.687988180587205</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.125813324295649</v>
+        <v>2.10436924647027</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.79222376947042</v>
+        <v>-8.66223272248695</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4041100818137253</v>
+        <v>-0.3521136630203374</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.687988180587205</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.121787019761245</v>
+        <v>2.100342941935867</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.175225158213051</v>
+        <v>-9.045234111229581</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5574127386323617</v>
+        <v>-0.5054163198389738</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.687988180587205</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.121684918439661</v>
+        <v>2.100240840614283</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.357094949198085</v>
+        <v>-9.227103902214616</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6275891390549457</v>
+        <v>-0.5755927202615578</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.834117841863276</v>
+        <v>-1.86985797157224</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.01513455982007</v>
+        <v>1.993690481994692</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.716625271702087</v>
+        <v>-9.586634224718617</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7660509647584961</v>
+        <v>-0.7140545459651082</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.834117841863276</v>
+        <v>-1.86985797157224</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.020484863118121</v>
+        <v>1.999040785292742</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.766974335156309</v>
+        <v>-9.636983288172839</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7782745701830076</v>
+        <v>-0.7262781513896193</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.884466905317498</v>
+        <v>-1.920207035026462</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.998191445002765</v>
+        <v>1.976747367177387</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.864593612577705</v>
+        <v>-9.734602565594235</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8142805305297971</v>
+        <v>-0.7622841117364092</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.982086182738895</v>
+        <v>-2.017826312447859</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.942661629171695</v>
+        <v>1.921217551346317</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.01211970058335</v>
+        <v>-9.882128653599878</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8703974094104816</v>
+        <v>-0.8184009906170941</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.129612270744539</v>
+        <v>-2.165352400453502</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.857039532689882</v>
+        <v>1.835595454864503</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.21637787591321</v>
+        <v>-10.08638682892974</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9465874824237854</v>
+        <v>-0.8945910636303971</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.257251215358528</v>
+        <v>-2.292991345067491</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.785969363040131</v>
+        <v>1.764525285214753</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.35818765012</v>
+        <v>-10.22819660313653</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9988288376220642</v>
+        <v>-0.9468324188286759</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.428530013004103</v>
+        <v>-2.464270142713067</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.687684638937222</v>
+        <v>1.666240561111843</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.28471781845255</v>
+        <v>-10.15472677146908</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9540692034616631</v>
+        <v>-0.9020727846682757</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.355060181336655</v>
+        <v>-2.390800311045618</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.747138239431112</v>
+        <v>1.725694161605734</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.45984223583909</v>
+        <v>-10.32985118885562</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.009563749668764</v>
+        <v>-0.957567330875376</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.530184598723198</v>
+        <v>-2.565924728432162</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.656618809746702</v>
+        <v>1.635174731921324</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.69429432985358</v>
+        <v>-10.56430328287011</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.110563752176156</v>
+        <v>-1.058567333382768</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.530184598723198</v>
+        <v>-2.565924728432162</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.649399644845106</v>
+        <v>1.627955567019728</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.98209817439082</v>
+        <v>-10.85210712740735</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.232357480765028</v>
+        <v>-1.180361061971639</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.817988443260437</v>
+        <v>-2.8537285729694</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.470045147348787</v>
+        <v>1.448601069523409</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.03488432999115</v>
+        <v>-10.90489328300768</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.252356153166602</v>
+        <v>-1.200359734373214</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.913663929842834</v>
+        <v>-2.949404059551797</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.413755645237905</v>
+        <v>1.392311567412527</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.16092112335944</v>
+        <v>-11.03093007637597</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.300077141884803</v>
+        <v>-1.248080723091415</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.924152436742055</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.431600347552865</v>
+        <v>1.410156269727487</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.10890560939063</v>
+        <v>-11.14527599877609</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.275280600610877</v>
+        <v>-1.289828756365065</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.924152436742055</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.435590683239266</v>
+        <v>1.414146605413888</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.25057745111475</v>
+        <v>-11.28694784050021</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.333424564199267</v>
+        <v>-1.347972719953455</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.924152436742055</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.434115456340525</v>
+        <v>1.412671378515146</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.20098660668991</v>
+        <v>-11.23735699607538</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.298534816264461</v>
+        <v>-1.313082972018649</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.838821462608257</v>
+        <v>-2.874561592317221</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.478923373160297</v>
+        <v>1.457479295334919</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.00183449945281</v>
+        <v>-11.03820488883828</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.231925107016304</v>
+        <v>-1.246473262770492</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.673498936658444</v>
+        <v>-2.709239066367408</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.565065755083502</v>
+        <v>1.543621677258124</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.7759893467334</v>
+        <v>-10.81235973611887</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.13200797289233</v>
+        <v>-1.146556128646519</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.63157226107128</v>
+        <v>-2.667312390780244</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.599800833472009</v>
+        <v>1.578356755646631</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.65141069039581</v>
+        <v>-10.68778107978128</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.081037365801235</v>
+        <v>-1.095585521555423</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.63157226107128</v>
+        <v>-2.667312390780244</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.600939978028068</v>
+        <v>1.57949590020269</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.70430597844009</v>
+        <v>-10.74067636782557</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.099561706856842</v>
+        <v>-1.114109862611031</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.626616914982834</v>
+        <v>-2.662357044691798</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.606546959843243</v>
+        <v>1.585102882017865</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42039724751135</v>
+        <v>-10.45676763689682</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9802645102467062</v>
+        <v>-0.994812666000894</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.626616914982834</v>
+        <v>-2.662357044691798</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.61228066408188</v>
+        <v>1.590836586256501</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.3490308549017</v>
+        <v>-10.38540124428717</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.961455215596712</v>
+        <v>-0.9760033713509007</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.59099065208215</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.645363237253803</v>
+        <v>1.623919159428425</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08519398769763</v>
+        <v>-10.1215643770831</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8658039500279915</v>
+        <v>-0.8803521057821801</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.59099065208215</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.635479755940896</v>
+        <v>1.614035678115517</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.817952186829231</v>
+        <v>-9.854322576214702</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7607417901800066</v>
+        <v>-0.7752899459341949</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.59099065208215</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.633645195441522</v>
+        <v>1.612201117616143</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.720045148152741</v>
+        <v>-9.756415537538212</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.721879289682871</v>
+        <v>-0.7364274454370596</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.48726477251263</v>
+        <v>-2.523004902221594</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.674136330384395</v>
+        <v>1.652692252559017</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.696091607176783</v>
+        <v>-9.732461996562254</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7116293671469944</v>
+        <v>-0.7261775229011826</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.463311231536672</v>
+        <v>-2.499051361245636</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.689176961115463</v>
+        <v>1.667732883290085</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.432031668853986</v>
+        <v>-9.468402058239457</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6192657079796278</v>
+        <v>-0.633813863733816</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.199251293213876</v>
+        <v>-2.23499142292284</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.834352607947389</v>
+        <v>1.81290853012201</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.724952045349148</v>
+        <v>-8.76132243473462</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3392208922379938</v>
+        <v>-0.353769047992182</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.199251293213876</v>
+        <v>-2.23499142292284</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.831565574287088</v>
+        <v>1.810121496461709</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.684767746982958</v>
+        <v>-8.721138136368429</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3228035490036762</v>
+        <v>-0.3373517047578645</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.159066994847685</v>
+        <v>-2.194807124556649</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.856019777194644</v>
+        <v>1.834575699369265</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.604697951445154</v>
+        <v>-8.641068340830625</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2914088095677974</v>
+        <v>-0.305956965321986</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.078997199309881</v>
+        <v>-2.114737329018845</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.903428475738083</v>
+        <v>1.881984397912704</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.371216729215554</v>
+        <v>-8.407587118601025</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1900918918381054</v>
+        <v>-0.2046400475922936</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.845515977080283</v>
+        <v>-1.881256106789247</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.051441637913695</v>
+        <v>2.029997560088316</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.22155033820804</v>
+        <v>-8.257920727593511</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1331175457480587</v>
+        <v>-0.1476657015022473</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.752612485837747</v>
+        <v>-1.788352615546711</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.104291522346257</v>
+        <v>2.082847444520878</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.089274864577153</v>
+        <v>-8.125645253962624</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08483986954867673</v>
+        <v>-0.09938802530286539</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.62033701220686</v>
+        <v>-1.656077141915824</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.179024293271816</v>
+        <v>2.157580215446437</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.898675189904</v>
+        <v>-7.935045579289471</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.005784938991778787</v>
+        <v>-0.02033309474596745</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.429737337533707</v>
+        <v>-1.465477467242671</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.296199158763344</v>
+        <v>2.274755080937966</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.649675391220419</v>
+        <v>-7.68604578060589</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.106721321705312</v>
+        <v>0.09217316595112379</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.429737337533707</v>
+        <v>-1.465477467242671</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.309105499987003</v>
+        <v>2.287661422161625</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.755265380993523</v>
+        <v>-7.791635770378995</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06349060380314819</v>
+        <v>-0.07803875955733686</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.535327327306812</v>
+        <v>-1.571067457015776</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.117775576523922</v>
+        <v>2.096331498698544</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.77400028311212</v>
+        <v>-7.810370672497592</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02244022277350055</v>
+        <v>-0.03698837852768921</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.535327327306812</v>
+        <v>-1.571067457015776</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.166319918401008</v>
+        <v>2.14487584057563</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.626060241704521</v>
+        <v>-7.662430631089992</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0831431288986284</v>
+        <v>-0.09769128465281707</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.515006411398254</v>
+        <v>-1.550746541107218</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.058633545257975</v>
+        <v>2.037189467432597</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.608902091573227</v>
+        <v>-7.645272480958698</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08499385509958923</v>
+        <v>-0.09954201085377745</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.533588390975924</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.060214449083273</v>
+        <v>2.038770371257895</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.565353684802536</v>
+        <v>-7.601724074188008</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07453510448640621</v>
+        <v>-0.08908326024059443</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.533588390975924</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.05325383698818</v>
+        <v>2.031809759162802</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.323205291348678</v>
+        <v>-7.359575680734149</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03678660727628014</v>
+        <v>0.02223845152209192</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.533588390975924</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.067716191369323</v>
+        <v>2.046272113543945</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.214946154226157</v>
+        <v>-7.251316543611628</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07462238258448384</v>
+        <v>0.06007422683029562</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.533588390975924</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.062248311828518</v>
+        <v>2.04080423400314</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.091655019409026</v>
+        <v>-7.128025408794497</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1214369305219134</v>
+        <v>0.1068887747677247</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.374557126449829</v>
+        <v>-1.410297256158793</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.133721086729374</v>
+        <v>2.112277008903996</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.070505820505582</v>
+        <v>-7.106876209891054</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1375975883206157</v>
+        <v>0.1230494325664271</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.353407927546386</v>
+        <v>-1.38914805725535</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.154111584308765</v>
+        <v>2.132667506483386</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.826740378522138</v>
+        <v>-6.863110767907609</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2308844734610442</v>
+        <v>0.2163363177068556</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.353407927546386</v>
+        <v>-1.38914805725535</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.149892292655815</v>
+        <v>2.128448214830437</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.679843350804267</v>
+        <v>-6.716213740189739</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2917675984682084</v>
+        <v>0.2772194427140198</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.341489815276762</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.180611551762984</v>
+        <v>2.159167473937606</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.429992956855193</v>
+        <v>-6.466363346240664</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3844498310315405</v>
+        <v>0.3699016752773518</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.341489815276762</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.173353626746687</v>
+        <v>2.151909548921308</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.254100864387761</v>
+        <v>-6.290471253773232</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4584057915391622</v>
+        <v>0.4438576357849735</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.341489815276762</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.176952750267335</v>
+        <v>2.155508672441957</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.082654401365297</v>
+        <v>-6.119024790750768</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5403118828027011</v>
+        <v>0.5257637270485125</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.134303222545335</v>
+        <v>-1.170043352254299</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.293148134135367</v>
+        <v>2.271704056309988</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.857621401696474</v>
+        <v>-5.893991791081945</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6293455602865272</v>
+        <v>0.614797404532339</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9092702228765118</v>
+        <v>-0.9450103525854759</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.427188411552958</v>
+        <v>2.405744333727579</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.79398565946254</v>
+        <v>-5.830356048848011</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6594946582344186</v>
+        <v>0.6449465024802299</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8456344806425773</v>
+        <v>-0.8813746103515414</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.470064657947636</v>
+        <v>2.448620580122257</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.700985618256642</v>
+        <v>-5.737356007642113</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6778889335005731</v>
+        <v>0.6633407777463849</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8456344806425773</v>
+        <v>-0.8813746103515414</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.451258916731431</v>
+        <v>2.429814838906053</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.460555121451781</v>
+        <v>-5.496925510837253</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7758042088473949</v>
+        <v>0.7612560530932062</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.605203983837717</v>
+        <v>-0.6409441135466811</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.597260291439225</v>
+        <v>2.575816213613846</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.388312553280587</v>
+        <v>-5.424682942666058</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8086305499506929</v>
+        <v>0.7940823941965043</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.605203983837717</v>
+        <v>-0.6409441135466811</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.601189605274045</v>
+        <v>2.579745527448666</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.335314230999199</v>
+        <v>-5.37168462038467</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8305084627805881</v>
+        <v>0.8159603070263994</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5498677248357782</v>
+        <v>-0.5856078545447423</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.635069944592548</v>
+        <v>2.61362586676717</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.226509345519472</v>
+        <v>-5.262879734904943</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8710284881924721</v>
+        <v>0.8564803324382839</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5498677248357782</v>
+        <v>-0.5856078545447423</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.632068015812542</v>
+        <v>2.610623937987163</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.006488547482461</v>
+        <v>-5.042858936867932</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9606158444178907</v>
+        <v>0.9460676886637023</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4086478797677979</v>
+        <v>-0.444388009476762</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.718378959863944</v>
+        <v>2.696934882038565</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.873620858419184</v>
+        <v>-4.909991247804655</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.029657102845025</v>
+        <v>1.015108947090837</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4086478797677979</v>
+        <v>-0.444388009476762</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.734273142665767</v>
+        <v>2.712829064840389</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.714105754899814</v>
+        <v>-4.750476144285285</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.094608988693075</v>
+        <v>1.080060832938886</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.249132776248428</v>
+        <v>-0.2848729059573921</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.831128049217691</v>
+        <v>2.809683971392313</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.569433609800076</v>
+        <v>-4.605803999185548</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.16256594929441</v>
+        <v>1.148017793540221</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1044606311486906</v>
+        <v>-0.1402007608576547</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.928019438838974</v>
+        <v>2.906575361013595</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.629308437157769</v>
+        <v>-4.66567882654324</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.124653509752759</v>
+        <v>1.11010535399857</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1643354585063827</v>
+        <v>-0.2000755882153468</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.878132033825784</v>
+        <v>2.856687956000405</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.542508939378759</v>
+        <v>-4.578879328764231</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.181773802186928</v>
+        <v>1.16722564643274</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1643354585063827</v>
+        <v>-0.2000755882153468</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.90053252714835</v>
+        <v>2.879088449322972</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.114446452171802</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.544978645840565</v>
+        <v>-4.581349035226037</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.180858320975618</v>
+        <v>1.28155041376764</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1668051649681889</v>
+        <v>-0.202545294677153</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.899123104644679</v>
+        <v>2.992919275365511</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.125453374646504</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.613348832164576</v>
+        <v>-4.649719221550047</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.164517168920716</v>
+        <v>1.265209261712738</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.193269595640938</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.915695446541109</v>
+        <v>3.009491617261941</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.115890083278395</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.72188701308071</v>
+        <v>-4.758257402466181</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.111538605186154</v>
+        <v>1.212230697978176</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.193269595640938</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.906132155173001</v>
+        <v>2.999928325893833</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.940599648318782</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.752880172409415</v>
+        <v>-4.789250561794886</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9238509064950584</v>
+        <v>1.02454299928708</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.193269595640938</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.730841720213387</v>
+        <v>2.824637890934219</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.94516688031057</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.577405912616946</v>
+        <v>-4.613776302002417</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9986078424038336</v>
+        <v>1.099299935195855</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.193269595640938</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.735408952205175</v>
+        <v>2.829205122926007</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.920908909071777</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.688342165258195</v>
+        <v>-4.724712554643666</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9299753701085411</v>
+        <v>1.030667462900563</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.193269595640938</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.711150980966382</v>
+        <v>2.804947151687214</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.924040294291682</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.891368742801428</v>
+        <v>-4.9277391321869</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8518961243111534</v>
+        <v>0.9525882171031752</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.3962961731841714</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.592466419660348</v>
+        <v>2.68626259038118</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.78434395226416</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.934212680723815</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.733443143866135</v>
+        <v>-4.769813533251607</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9252387503174031</v>
+        <v>1.025930843109425</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.3962961731841714</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.60263880609248</v>
+        <v>2.696434976813312</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.929158951297675</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.647199680839758</v>
+        <v>-4.683570070225229</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9546824061018144</v>
+        <v>1.055374498893836</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.3962961731841714</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.59758507666634</v>
+        <v>2.691381247387172</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.920934726742201</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.692506500238737</v>
+        <v>-4.728876889624209</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9283354537867481</v>
+        <v>1.02902754657877</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4013662064844381</v>
+        <v>-0.4371063361934022</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.564874754305328</v>
+        <v>2.65867092502616</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.921486599775302</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.721539604941039</v>
+        <v>-4.75790999432651</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9172740849389291</v>
+        <v>1.017966177730951</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4013662064844381</v>
+        <v>-0.4371063361934022</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.565426627338429</v>
+        <v>2.659222798059261</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.850759291666668</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.628729123490179</v>
+        <v>-4.66509951287565</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8836709694106386</v>
+        <v>0.9843630622026605</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3085557250335788</v>
+        <v>-0.3442958547425429</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.55038560810031</v>
+        <v>2.644181778821142</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.852632767591269</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.673118592819606</v>
+        <v>-4.709488982205078</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8677886576034686</v>
+        <v>0.9684807503954902</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3529451943630064</v>
+        <v>-0.3886853240719705</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.525625402427255</v>
+        <v>2.619421573148086</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.847708476102992</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.560447374583356</v>
+        <v>-4.596817763968827</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9079328534096915</v>
+        <v>1.008624946201713</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2402739761267562</v>
+        <v>-0.2760141058357203</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.588303841880728</v>
+        <v>2.68210001260156</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.853199771933659</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.448070373400683</v>
+        <v>-4.484440762786154</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.958374949713428</v>
+        <v>1.05906704250545</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2402739761267562</v>
+        <v>-0.2760141058357203</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.593795137711395</v>
+        <v>2.687591308432227</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.864696973702198</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.646304942287414</v>
+        <v>-4.682675331672885</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8905783239272747</v>
+        <v>0.9912704167192965</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4385085450134868</v>
+        <v>-0.4742486747224509</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.486351598147896</v>
+        <v>2.580147768868728</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.703052693702851</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.729306223312693</v>
+        <v>-4.765676612698164</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6957335315178164</v>
+        <v>0.7964256243098382</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.4928195592496247</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.313564787432245</v>
+        <v>2.407360958153077</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.823202354422057</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.856373229619681</v>
+        <v>-4.892743619005152</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7650563897142268</v>
+        <v>0.8657484825062487</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.4928195592496247</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.43371444815145</v>
+        <v>2.527510618872282</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.83771538052438</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.942971812600784</v>
+        <v>-4.979342201986255</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7449299826241087</v>
+        <v>0.8456220754161303</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.4928195592496247</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.448227474253773</v>
+        <v>2.542023644974605</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.835134821866748</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.904588150042633</v>
+        <v>-4.940958539428104</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7577028889897377</v>
+        <v>0.8583949817817595</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4186957669825094</v>
+        <v>-0.4544358966914735</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.468677113131033</v>
+        <v>2.562473283851864</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.83186385071205</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.727471820007467</v>
+        <v>-4.763842209392938</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8252784498491061</v>
+        <v>0.925970542641128</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4186957669825094</v>
+        <v>-0.4544358966914735</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.465406141976335</v>
+        <v>2.559202312697167</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.832547242473964</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.697769696031173</v>
+        <v>-4.734140085416644</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8378426912015366</v>
+        <v>0.9385347839935585</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4231658921978227</v>
+        <v>-0.4589060219067869</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.46340745860906</v>
+        <v>2.557203629329892</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.826334217780378</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.518394274792406</v>
+        <v>-4.554764664177877</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9033798350034581</v>
+        <v>1.00407192779548</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2663891340271041</v>
+        <v>-0.3021292637360682</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.551260488817905</v>
+        <v>2.645056659538737</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.807141673111968</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.563408488313012</v>
+        <v>-4.599778877698483</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8661816049268052</v>
+        <v>0.966873697718827</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2967380293417087</v>
+        <v>-0.3324781590506728</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.513858606960732</v>
+        <v>2.607654777681564</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.812833235450913</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.830412998585447</v>
+        <v>-4.866783387970918</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7650713631567769</v>
+        <v>0.8657634559487988</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4911010673846573</v>
+        <v>-0.5268411970936213</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.402932346473909</v>
+        <v>2.496728517194741</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.812037157347415</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.93161078002262</v>
+        <v>-4.967981169408091</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7237961724784092</v>
+        <v>0.8244882652704311</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5595098809299764</v>
+        <v>-0.5952500106389405</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.361090980243219</v>
+        <v>2.454887150964051</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.809637118901732</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.899135193851848</v>
+        <v>-4.935505583237319</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7343863685010348</v>
+        <v>0.8350784612930566</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5595098809299764</v>
+        <v>-0.5952500106389405</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.358690941797536</v>
+        <v>2.452487112518368</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.806161838109976</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.88009706614455</v>
+        <v>-4.916467455530022</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7385263387921988</v>
+        <v>0.8392184315842206</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.617693492261171</v>
+        <v>-0.653433621970135</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.320305494207064</v>
+        <v>2.414101664927896</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.983743707048657</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.911223697295169</v>
+        <v>-4.94759408668064</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9036575552706319</v>
+        <v>1.004349648062654</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.617693492261171</v>
+        <v>-0.653433621970135</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.497887363145745</v>
+        <v>2.591683533866576</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.984577036034791</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.963544077895961</v>
+        <v>-4.999914467281432</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8835627320164487</v>
+        <v>0.9842548248084706</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5827466322522988</v>
+        <v>-0.6184867619612628</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.519688808137201</v>
+        <v>2.613484978858033</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.990585566431716</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.107866983820879</v>
+        <v>-5.144237373206351</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8318421000434073</v>
+        <v>0.9325341928354289</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5827466322522988</v>
+        <v>-0.6184867619612628</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.525697338534127</v>
+        <v>2.619493509254959</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.069738214223738</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.960124013585877</v>
+        <v>-4.996494402971348</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.97009193592943</v>
+        <v>1.070784028721452</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4149392750174157</v>
+        <v>-0.4506794047263797</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.705534400667079</v>
+        <v>2.799330571387911</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.072531835755219</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.062138696117098</v>
+        <v>-5.098509085502569</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9320796844484227</v>
+        <v>1.032771777240444</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4149392750174157</v>
+        <v>-0.4506794047263797</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.70832802219856</v>
+        <v>2.802124192919392</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.073194184146878</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.925529352023005</v>
+        <v>-4.961899741408477</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.987385770477718</v>
+        <v>1.08807786326974</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2783299309233232</v>
+        <v>-0.3140700606322872</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.790955977046674</v>
+        <v>2.884752147767506</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.072274660886988</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.068294684845656</v>
+        <v>-5.104665074231127</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9293601140887682</v>
+        <v>1.03005220688079</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4210952637459736</v>
+        <v>-0.4568353934549376</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.704377254093194</v>
+        <v>2.798173424814026</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.138610214683809</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.005996686069533</v>
+        <v>-5.042367075455005</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.020614867396038</v>
+        <v>1.12130696018806</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4210952637459736</v>
+        <v>-0.4568353934549376</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.770712807890015</v>
+        <v>2.864508978610846</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.847191087073207</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.804206488404375</v>
+        <v>-4.840576877789847</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8099118188514991</v>
+        <v>0.9106039116435209</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2230770715768192</v>
+        <v>-0.2588172012857832</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.598104595580905</v>
+        <v>2.691900766301737</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.917481319395382</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.744315806761782</v>
+        <v>-4.780686196147253</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9041583238307118</v>
+        <v>1.004850416622733</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1631863899342257</v>
+        <v>-0.1989265196431897</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.704329236888637</v>
+        <v>2.798125407609469</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.932109055511426</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.842056351386756</v>
+        <v>-4.878426740772228</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8796898420967656</v>
+        <v>0.9803819348887874</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1790756680672059</v>
+        <v>-0.2148157977761699</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.709423406124892</v>
+        <v>2.803219576845724</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.930645036336097</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.018394111509686</v>
+        <v>-5.054764500895157</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8076907188722657</v>
+        <v>0.9083828116642874</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3554134281901353</v>
+        <v>-0.3911535578990993</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.602156730875806</v>
+        <v>2.695952901596638</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.929136654376026</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.017704739348463</v>
+        <v>-5.054075128733934</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8064580857766832</v>
+        <v>0.9071501785687053</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3554134281901353</v>
+        <v>-0.3911535578990993</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.600648348915735</v>
+        <v>2.694444519636567</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.928999521811462</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.024275704403055</v>
+        <v>-5.060646093788526</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8036925671902826</v>
+        <v>0.9043846599823042</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3619843932447283</v>
+        <v>-0.3977245229536923</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.596568637318415</v>
+        <v>2.690364808039247</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.928999521811462</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.016321734108283</v>
+        <v>-5.052692123493754</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8068741553081913</v>
+        <v>0.9075662481002134</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3619843932447283</v>
+        <v>-0.3977245229536923</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.596568637318415</v>
+        <v>2.690364808039247</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.935381278839267</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.005948357775196</v>
+        <v>-5.042318747160667</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8174052628692308</v>
+        <v>0.9180973556612524</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.351611016911641</v>
+        <v>-0.387351146620605</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.609174420146072</v>
+        <v>2.702970590866904</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.940273652213992</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.8782640479809</v>
+        <v>-4.914634437366371</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8733713601616742</v>
+        <v>0.974063452953696</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2239267071173445</v>
+        <v>-0.2596668368263085</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.690677379397375</v>
+        <v>2.784473550118207</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.927028324689864</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.938930638383288</v>
+        <v>-4.97530102776876</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8358593964765908</v>
+        <v>0.9365514892686126</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3056250238358782</v>
+        <v>-0.3413651535448422</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.628413061842127</v>
+        <v>2.722209232562959</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.931126027300492</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.873936778449643</v>
+        <v>-4.910307167835114</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8659546430606777</v>
+        <v>0.9666467358526996</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2787944092317228</v>
+        <v>-0.3145345389406868</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.648609133215249</v>
+        <v>2.742405303936081</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674305</v>
+        <v>3.817961388674306</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.93528696693157</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.974695414206641</v>
+        <v>-5.011065803592112</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8298121283889563</v>
+        <v>0.9305042211809784</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3676199779587283</v>
+        <v>-0.4033601076676923</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.599474731610123</v>
+        <v>2.693270902330955</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.581042179381063</v>
+        <v>3.748975463424548</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.704115520070538</v>
+        <v>2.778926119002515</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.974695414206641</v>
+        <v>-5.011065803592112</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8298121283889563</v>
+        <v>0.9305042211809784</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3676199779587283</v>
+        <v>-0.4033601076676923</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.697179317056905</v>
+        <v>2.771989915988883</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-678.4%</t>
+          <t>-674.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.0%</t>
+          <t>451.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.7%</t>
+          <t>-643.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-271.8%</t>
+          <t>-270.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>169.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.2%</t>
+          <t>-286.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.6%</t>
+          <t>-302.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.0%</t>
+          <t>-147.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.3%</t>
+          <t>-247.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.8%</t>
+          <t>-181.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.8%</t>
+          <t>-177.5%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9830893725955661</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.725561385093993</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.239343078854473</v>
+        <v>1.275083208563437</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.86275940575865</v>
+        <v>3.884203483584028</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.400843396142403</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.556386667180321</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8215890553076358</v>
+        <v>0.8573291850165997</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.610033883135611</v>
+        <v>3.631477960960989</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.604132865464206</v>
+        <v>-1.568392735755242</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.474937096050521</v>
+        <v>2.489233147934107</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8596684660732076</v>
+        <v>0.8954085957821715</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.632747746193876</v>
+        <v>3.654191824019255</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.812136923817283</v>
+        <v>-1.776396794108319</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.396627617263216</v>
+        <v>2.410923669146801</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8596684660732076</v>
+        <v>0.8954085957821715</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.637639890747801</v>
+        <v>3.65908396857318</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.023549344705258</v>
+        <v>-1.987809214996294</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.307144105246014</v>
+        <v>2.3214401571296</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6482560451852325</v>
+        <v>0.6839961748941964</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.505873894553004</v>
+        <v>3.527317972378383</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.36270772229378</v>
+        <v>-2.326967592584817</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.164565053517054</v>
+        <v>2.17886110540064</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3090976675967104</v>
+        <v>0.3448377973056743</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29546316730634</v>
+        <v>3.316907245131719</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.571198503745465</v>
+        <v>-2.535458374036501</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.101507030675148</v>
+        <v>2.115803082558734</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.100606886145026</v>
+        <v>0.1363470158539899</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.190706988174098</v>
+        <v>3.212151065999476</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.818399688510686</v>
+        <v>-2.782659558801723</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.010725307177629</v>
+        <v>2.025021359061214</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1207602396438384</v>
+        <v>0.1565003693528023</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.210897750681954</v>
+        <v>3.232341828507332</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.310784716534783</v>
+        <v>-3.27504458682582</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.814877688011722</v>
+        <v>1.829173739895307</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3716247883802583</v>
+        <v>-0.3358846586712944</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.916573125911228</v>
+        <v>2.938017203736606</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.695965107464855</v>
+        <v>-3.660224977755892</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.659348070452557</v>
+        <v>1.673644122336142</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3716247883802583</v>
+        <v>-0.3358846586712944</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.915115664724091</v>
+        <v>2.936559742549469</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.039647880691518</v>
+        <v>-4.003907750982555</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.523644084616508</v>
+        <v>1.537940136500093</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4795308404074765</v>
+        <v>-0.4437907106985126</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.852141156962376</v>
+        <v>2.873585234787755</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.24615965757854</v>
+        <v>-4.210419527869576</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.437145432517957</v>
+        <v>1.451441484401542</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.686042617294498</v>
+        <v>-0.6503024875855341</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.724340149486421</v>
+        <v>2.7457842273118</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.502000743357232</v>
+        <v>-4.466260613648269</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.336581924906739</v>
+        <v>1.350877976790325</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.686042617294498</v>
+        <v>-0.6503024875855341</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.726113076186681</v>
+        <v>2.747557154012059</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.93380653650702</v>
+        <v>-4.898066406798057</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.150192495114229</v>
+        <v>1.164488546997814</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.822460113735765</v>
+        <v>-0.7867199840268011</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.630595465789325</v>
+        <v>2.652039543614704</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.168500530639572</v>
+        <v>-5.132760400930609</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.044599672463298</v>
+        <v>1.058895724346884</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8161238465065098</v>
+        <v>-0.7803837167975459</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.622682001128969</v>
+        <v>2.644126078954347</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.504163177870025</v>
+        <v>-5.468423048161061</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9089152052270824</v>
+        <v>0.9232112571106676</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8161238465065098</v>
+        <v>-0.7803837167975459</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.621262592784934</v>
+        <v>2.642706670610313</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.867789422770338</v>
+        <v>-5.832049293061375</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7699522675011989</v>
+        <v>0.7842483193847842</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9143454833736356</v>
+        <v>-0.8786053536646717</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.5688171708989</v>
+        <v>2.590261248724278</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.232916805409085</v>
+        <v>-6.197176675700121</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6231558294515316</v>
+        <v>0.6374518813351169</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.210656267672648</v>
+        <v>-1.174916137963684</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.390285215325324</v>
+        <v>2.411729293150702</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.641505582589764</v>
+        <v>-6.605765452880799</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4584818625940188</v>
+        <v>0.4727779144776045</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.143893493031676</v>
+        <v>2.165337570857054</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.918081682905596</v>
+        <v>-6.882341553196632</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3430368549391467</v>
+        <v>0.357332906822732</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.139078925503137</v>
+        <v>2.160523003328515</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.334473557192593</v>
+        <v>-7.298733427483629</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.174474155833225</v>
+        <v>0.1887702077168107</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.137072976112014</v>
+        <v>2.158517053937392</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.651085499733242</v>
+        <v>-7.615345370024277</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05808806948564449</v>
+        <v>0.07238412136923023</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.147331666780693</v>
+        <v>2.168775744606071</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.996960321718051</v>
+        <v>-7.961220192009087</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0841622941625837</v>
+        <v>-0.0698662422789984</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.143431231926388</v>
+        <v>2.164875309751767</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.160540199902435</v>
+        <v>-8.124800070193471</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1511893253813366</v>
+        <v>-0.1368932734977508</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.619245044853327</v>
+        <v>-1.583504915144363</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.141836151981389</v>
+        <v>2.163280229806768</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.457201541712633</v>
+        <v>-8.421461412003669</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2660748861762077</v>
+        <v>-0.2517788342926219</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.687988180587205</v>
+        <v>-1.652248050878241</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.10436924647027</v>
+        <v>2.125813324295649</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.66223272248695</v>
+        <v>-8.626492592777986</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3521136630203374</v>
+        <v>-0.3378176111367517</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.687988180587205</v>
+        <v>-1.652248050878241</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.100342941935867</v>
+        <v>2.121787019761245</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.045234111229581</v>
+        <v>-9.009493981520617</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5054163198389738</v>
+        <v>-0.4911202679553881</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.687988180587205</v>
+        <v>-1.652248050878241</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.100240840614283</v>
+        <v>2.121684918439661</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.227103902214616</v>
+        <v>-9.191363772505651</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5755927202615578</v>
+        <v>-0.5612966683779721</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.86985797157224</v>
+        <v>-1.834117841863276</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.993690481994692</v>
+        <v>2.01513455982007</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.586634224718617</v>
+        <v>-9.550894095009653</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7140545459651082</v>
+        <v>-0.6997584940815225</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.86985797157224</v>
+        <v>-1.834117841863276</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.999040785292742</v>
+        <v>2.020484863118121</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.636983288172839</v>
+        <v>-9.601243158463875</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7262781513896193</v>
+        <v>-0.711982099506034</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.920207035026462</v>
+        <v>-1.884466905317498</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.976747367177387</v>
+        <v>1.998191445002765</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.734602565594235</v>
+        <v>-9.698862435885271</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7622841117364092</v>
+        <v>-0.7479880598528235</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.017826312447859</v>
+        <v>-1.982086182738895</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.921217551346317</v>
+        <v>1.942661629171695</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.882128653599878</v>
+        <v>-9.846388523890914</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8184009906170941</v>
+        <v>-0.8041049387335084</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.165352400453502</v>
+        <v>-2.129612270744539</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.835595454864503</v>
+        <v>1.857039532689882</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.08638682892974</v>
+        <v>-10.05064669922078</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8945910636303971</v>
+        <v>-0.8802950117468118</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.292991345067491</v>
+        <v>-2.257251215358528</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.764525285214753</v>
+        <v>1.785969363040131</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.22819660313653</v>
+        <v>-10.19245647342757</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9468324188286759</v>
+        <v>-0.9325363669450906</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.464270142713067</v>
+        <v>-2.428530013004103</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.666240561111843</v>
+        <v>1.687684638937222</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.15472677146908</v>
+        <v>-10.11898664176012</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9020727846682757</v>
+        <v>-0.8877767327846895</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.390800311045618</v>
+        <v>-2.355060181336655</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.725694161605734</v>
+        <v>1.747138239431112</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.32985118885562</v>
+        <v>-10.29411105914666</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.957567330875376</v>
+        <v>-0.9432712789917908</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.565924728432162</v>
+        <v>-2.530184598723198</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.635174731921324</v>
+        <v>1.656618809746702</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.56430328287011</v>
+        <v>-10.52856315316115</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.058567333382768</v>
+        <v>-1.044271281499182</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.565924728432162</v>
+        <v>-2.530184598723198</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.627955567019728</v>
+        <v>1.649399644845106</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85210712740735</v>
+        <v>-10.81636699769839</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.180361061971639</v>
+        <v>-1.166065010088054</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.8537285729694</v>
+        <v>-2.817988443260437</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.448601069523409</v>
+        <v>1.470045147348787</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.90489328300768</v>
+        <v>-10.86915315329871</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.200359734373214</v>
+        <v>-1.186063682489628</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.949404059551797</v>
+        <v>-2.913663929842834</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.392311567412527</v>
+        <v>1.413755645237905</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03093007637597</v>
+        <v>-10.995189946667</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.248080723091415</v>
+        <v>-1.233784671207829</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.924152436742055</v>
+        <v>-2.888412307033091</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.410156269727487</v>
+        <v>1.431600347552865</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.14527599877609</v>
+        <v>-10.94317443269819</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.289828756365065</v>
+        <v>-1.208988129933903</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.924152436742055</v>
+        <v>-2.888412307033091</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.414146605413888</v>
+        <v>1.435590683239266</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.28694784050021</v>
+        <v>-11.08484627442231</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.347972719953455</v>
+        <v>-1.267132093522293</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.924152436742055</v>
+        <v>-2.888412307033091</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.412671378515146</v>
+        <v>1.434115456340525</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.23735699607538</v>
+        <v>-11.03525542999748</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.313082972018649</v>
+        <v>-1.232242345587487</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.874561592317221</v>
+        <v>-2.838821462608257</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.457479295334919</v>
+        <v>1.478923373160297</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.03820488883828</v>
+        <v>-10.83610332276038</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.246473262770492</v>
+        <v>-1.165632636339331</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.709239066367408</v>
+        <v>-2.673498936658444</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.543621677258124</v>
+        <v>1.565065755083502</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.81235973611887</v>
+        <v>-10.61025817004097</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.146556128646519</v>
+        <v>-1.065715502215358</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.667312390780244</v>
+        <v>-2.63157226107128</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.578356755646631</v>
+        <v>1.599800833472009</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.68778107978128</v>
+        <v>-10.48567951370338</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.095585521555423</v>
+        <v>-1.014744895124262</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.667312390780244</v>
+        <v>-2.63157226107128</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.57949590020269</v>
+        <v>1.600939978028068</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.74067636782557</v>
+        <v>-10.53857480174766</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.114109862611031</v>
+        <v>-1.033269236179869</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.662357044691798</v>
+        <v>-2.626616914982834</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.585102882017865</v>
+        <v>1.606546959843243</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.45676763689682</v>
+        <v>-10.25466607081891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.994812666000894</v>
+        <v>-0.9139720395697326</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.662357044691798</v>
+        <v>-2.626616914982834</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.590836586256501</v>
+        <v>1.61228066408188</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.38540124428717</v>
+        <v>-10.18329967820927</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9760033713509007</v>
+        <v>-0.8951627449197392</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.59099065208215</v>
+        <v>-2.555250522373186</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.623919159428425</v>
+        <v>1.645363237253803</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.1215643770831</v>
+        <v>-9.919462811005197</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8803521057821801</v>
+        <v>-0.7995114793510187</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.59099065208215</v>
+        <v>-2.555250522373186</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.614035678115517</v>
+        <v>1.635479755940896</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.854322576214702</v>
+        <v>-9.652221010136799</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7752899459341949</v>
+        <v>-0.6944493195030335</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.59099065208215</v>
+        <v>-2.555250522373186</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.612201117616143</v>
+        <v>1.633645195441522</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.756415537538212</v>
+        <v>-9.554313971460308</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7364274454370596</v>
+        <v>-0.6555868190058982</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.523004902221594</v>
+        <v>-2.48726477251263</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.652692252559017</v>
+        <v>1.674136330384395</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.732461996562254</v>
+        <v>-9.53036043048435</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7261775229011826</v>
+        <v>-0.6453368964700212</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.499051361245636</v>
+        <v>-2.463311231536672</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.667732883290085</v>
+        <v>1.689176961115463</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.468402058239457</v>
+        <v>-9.266300492161553</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.633813863733816</v>
+        <v>-0.5529732373026546</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.23499142292284</v>
+        <v>-2.199251293213876</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.81290853012201</v>
+        <v>1.834352607947389</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.76132243473462</v>
+        <v>-8.559220868656716</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.353769047992182</v>
+        <v>-0.2729284215610206</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.23499142292284</v>
+        <v>-2.199251293213876</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.810121496461709</v>
+        <v>1.831565574287088</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.721138136368429</v>
+        <v>-8.519036570290526</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3373517047578645</v>
+        <v>-0.2565110783267031</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.194807124556649</v>
+        <v>-2.159066994847685</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.834575699369265</v>
+        <v>1.856019777194644</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.641068340830625</v>
+        <v>-8.438966774752721</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.305956965321986</v>
+        <v>-0.2251163388908246</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.114737329018845</v>
+        <v>-2.078997199309881</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.881984397912704</v>
+        <v>1.903428475738083</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.407587118601025</v>
+        <v>-8.205485552523122</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2046400475922936</v>
+        <v>-0.1237994211611322</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.881256106789247</v>
+        <v>-1.845515977080283</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.029997560088316</v>
+        <v>2.051441637913695</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.257920727593511</v>
+        <v>-8.055819161515608</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1476657015022473</v>
+        <v>-0.06682507507108593</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.788352615546711</v>
+        <v>-1.752612485837747</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.082847444520878</v>
+        <v>2.104291522346257</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.125645253962624</v>
+        <v>-7.923543687884721</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.09938802530286539</v>
+        <v>-0.01854739887170398</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.656077141915824</v>
+        <v>-1.62033701220686</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.157580215446437</v>
+        <v>2.179024293271816</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.935045579289471</v>
+        <v>-7.732944013211569</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02033309474596745</v>
+        <v>0.06050753168519352</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.465477467242671</v>
+        <v>-1.429737337533707</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.274755080937966</v>
+        <v>2.296199158763344</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.68604578060589</v>
+        <v>-7.483944214527988</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09217316595112379</v>
+        <v>0.1730137923822848</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.465477467242671</v>
+        <v>-1.429737337533707</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.287661422161625</v>
+        <v>2.309105499987003</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.791635770378995</v>
+        <v>-7.589534204301092</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.07803875955733686</v>
+        <v>0.00280186687382411</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.571067457015776</v>
+        <v>-1.535327327306812</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.096331498698544</v>
+        <v>2.117775576523922</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.810370672497592</v>
+        <v>-7.608269106419689</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03698837852768921</v>
+        <v>0.04385224790347175</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.571067457015776</v>
+        <v>-1.535327327306812</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.14487584057563</v>
+        <v>2.166319918401008</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.662430631089992</v>
+        <v>-7.46032906501209</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.09769128465281707</v>
+        <v>-0.0168506582216561</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.550746541107218</v>
+        <v>-1.515006411398254</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.037189467432597</v>
+        <v>2.058633545257975</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.645272480958698</v>
+        <v>-7.443170914880795</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09954201085377745</v>
+        <v>-0.01870138442261648</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.533588390975924</v>
+        <v>-1.49784826126696</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.038770371257895</v>
+        <v>2.060214449083273</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.601724074188008</v>
+        <v>-7.399622508110105</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08908326024059443</v>
+        <v>-0.008242633809433464</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.533588390975924</v>
+        <v>-1.49784826126696</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.031809759162802</v>
+        <v>2.05325383698818</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.359575680734149</v>
+        <v>-7.157474114656247</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02223845152209192</v>
+        <v>0.1030790779532529</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.533588390975924</v>
+        <v>-1.49784826126696</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.046272113543945</v>
+        <v>2.067716191369323</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.251316543611628</v>
+        <v>-7.049214977533725</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06007422683029562</v>
+        <v>0.1409148532614566</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.533588390975924</v>
+        <v>-1.49784826126696</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.04080423400314</v>
+        <v>2.062248311828518</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.128025408794497</v>
+        <v>-6.925923842716594</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1068887747677247</v>
+        <v>0.1877294011988857</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.410297256158793</v>
+        <v>-1.374557126449829</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.112277008903996</v>
+        <v>2.133721086729374</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.106876209891054</v>
+        <v>-6.904774643813151</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1230494325664271</v>
+        <v>0.2038900589975885</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.38914805725535</v>
+        <v>-1.353407927546386</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.132667506483386</v>
+        <v>2.154111584308765</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.863110767907609</v>
+        <v>-6.661009201829707</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2163363177068556</v>
+        <v>0.2971769441380165</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.38914805725535</v>
+        <v>-1.353407927546386</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.128448214830437</v>
+        <v>2.149892292655815</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.716213740189739</v>
+        <v>-6.514112174111837</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2772194427140198</v>
+        <v>0.3580600691451807</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.341489815276762</v>
+        <v>-1.305749685567798</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.159167473937606</v>
+        <v>2.180611551762984</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.466363346240664</v>
+        <v>-6.264261780162762</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3699016752773518</v>
+        <v>0.4507423017085128</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.341489815276762</v>
+        <v>-1.305749685567798</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.151909548921308</v>
+        <v>2.173353626746687</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.290471253773232</v>
+        <v>-6.08836968769533</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4438576357849735</v>
+        <v>0.524698262216134</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.341489815276762</v>
+        <v>-1.305749685567798</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.155508672441957</v>
+        <v>2.176952750267335</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.119024790750768</v>
+        <v>-5.916923224672867</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5257637270485125</v>
+        <v>0.6066043534796735</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.170043352254299</v>
+        <v>-1.134303222545335</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.271704056309988</v>
+        <v>2.293148134135367</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.893991791081945</v>
+        <v>-5.691890225004044</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.614797404532339</v>
+        <v>0.6956380309634995</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9450103525854759</v>
+        <v>-0.9092702228765118</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.405744333727579</v>
+        <v>2.427188411552958</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.830356048848011</v>
+        <v>-5.628254482770109</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6449465024802299</v>
+        <v>0.7257871289113904</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8813746103515414</v>
+        <v>-0.8456344806425773</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.448620580122257</v>
+        <v>2.470064657947636</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.737356007642113</v>
+        <v>-5.535254441564211</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6633407777463849</v>
+        <v>0.7441814041775454</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8813746103515414</v>
+        <v>-0.8456344806425773</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.429814838906053</v>
+        <v>2.451258916731431</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.496925510837253</v>
+        <v>-5.294823944759351</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7612560530932062</v>
+        <v>0.8420966795243672</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6409441135466811</v>
+        <v>-0.605203983837717</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.575816213613846</v>
+        <v>2.597260291439225</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.424682942666058</v>
+        <v>-5.222581376588156</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7940823941965043</v>
+        <v>0.8749230206276652</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6409441135466811</v>
+        <v>-0.605203983837717</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.579745527448666</v>
+        <v>2.601189605274045</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.37168462038467</v>
+        <v>-5.169583054306768</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8159603070263994</v>
+        <v>0.8968009334575604</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5856078545447423</v>
+        <v>-0.5498677248357782</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.61362586676717</v>
+        <v>2.635069944592548</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.262879734904943</v>
+        <v>-5.060778168827041</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8564803324382839</v>
+        <v>0.9373209588694444</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5856078545447423</v>
+        <v>-0.5498677248357782</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.610623937987163</v>
+        <v>2.632068015812542</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.042858936867932</v>
+        <v>-4.840757370790031</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9460676886637023</v>
+        <v>1.026908315094863</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.444388009476762</v>
+        <v>-0.4086478797677979</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.696934882038565</v>
+        <v>2.718378959863944</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.909991247804655</v>
+        <v>-4.707889681726753</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.015108947090837</v>
+        <v>1.095949573521997</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.444388009476762</v>
+        <v>-0.4086478797677979</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.712829064840389</v>
+        <v>2.734273142665767</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.750476144285285</v>
+        <v>-4.548374578207383</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.080060832938886</v>
+        <v>1.160901459370047</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2848729059573921</v>
+        <v>-0.249132776248428</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.809683971392313</v>
+        <v>2.831128049217691</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.605803999185548</v>
+        <v>-4.403702433107646</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.148017793540221</v>
+        <v>1.228858419971382</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1402007608576547</v>
+        <v>-0.1044606311486906</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.906575361013595</v>
+        <v>2.928019438838974</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.66567882654324</v>
+        <v>-4.463577260465338</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.11010535399857</v>
+        <v>1.190945980429731</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2000755882153468</v>
+        <v>-0.1643354585063827</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.856687956000405</v>
+        <v>2.878132033825784</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.578879328764231</v>
+        <v>-4.376777762686329</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.16722564643274</v>
+        <v>1.2480662728639</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2000755882153468</v>
+        <v>-0.1643354585063827</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.879088449322972</v>
+        <v>2.90053252714835</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.114446452171802</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.581349035226037</v>
+        <v>-4.379247469148135</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.28155041376764</v>
+        <v>1.24715079165259</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.202545294677153</v>
+        <v>-0.1668051649681889</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.992919275365511</v>
+        <v>2.899123104644679</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.125453374646504</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.649719221550047</v>
+        <v>-4.447617655472145</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.265209261712738</v>
+        <v>1.230809639597688</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.193269595640938</v>
+        <v>-0.1575294659319739</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.009491617261941</v>
+        <v>2.915695446541109</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.115890083278395</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.758257402466181</v>
+        <v>-4.556155836388279</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.212230697978176</v>
+        <v>1.177831075863126</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.193269595640938</v>
+        <v>-0.1575294659319739</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.999928325893833</v>
+        <v>2.906132155173001</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.940599648318782</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.789250561794886</v>
+        <v>-4.587148995716984</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.02454299928708</v>
+        <v>0.9901433771720307</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.193269595640938</v>
+        <v>-0.1575294659319739</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.824637890934219</v>
+        <v>2.730841720213387</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.94516688031057</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.613776302002417</v>
+        <v>-4.411674735924516</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099299935195855</v>
+        <v>1.064900313080806</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.193269595640938</v>
+        <v>-0.1575294659319739</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.829205122926007</v>
+        <v>2.735408952205175</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.920908909071777</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.724712554643666</v>
+        <v>-4.522610988565765</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.030667462900563</v>
+        <v>0.9962678407855134</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.193269595640938</v>
+        <v>-0.1575294659319739</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.804947151687214</v>
+        <v>2.711150980966382</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.924040294291682</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.9277391321869</v>
+        <v>-4.725637566108998</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9525882171031752</v>
+        <v>0.9181885949881257</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3962961731841714</v>
+        <v>-0.3605560434752073</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.68626259038118</v>
+        <v>2.592466419660348</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.78434395226416</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.934212680723815</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.769813533251607</v>
+        <v>-4.567711967173705</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.025930843109425</v>
+        <v>0.9915312209943752</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3962961731841714</v>
+        <v>-0.3605560434752073</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.696434976813312</v>
+        <v>2.60263880609248</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.929158951297675</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.683570070225229</v>
+        <v>-4.481468504147327</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.055374498893836</v>
+        <v>1.020974876778787</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3962961731841714</v>
+        <v>-0.3605560434752073</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.691381247387172</v>
+        <v>2.59758507666634</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.920934726742201</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.728876889624209</v>
+        <v>-4.526775323546307</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.02902754657877</v>
+        <v>0.9946279244637202</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4371063361934022</v>
+        <v>-0.4013662064844381</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.65867092502616</v>
+        <v>2.564874754305328</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.921486599775302</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.75790999432651</v>
+        <v>-4.555808428248608</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.017966177730951</v>
+        <v>0.9835665556159014</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4371063361934022</v>
+        <v>-0.4013662064844381</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.659222798059261</v>
+        <v>2.565426627338429</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.850759291666668</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.66509951287565</v>
+        <v>-4.462997946797748</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9843630622026605</v>
+        <v>0.9499634400876109</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3442958547425429</v>
+        <v>-0.3085557250335788</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.644181778821142</v>
+        <v>2.55038560810031</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.852632767591269</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.709488982205078</v>
+        <v>-4.507387416127176</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9684807503954902</v>
+        <v>0.9340811282804407</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3886853240719705</v>
+        <v>-0.3529451943630064</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.619421573148086</v>
+        <v>2.525625402427255</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.847708476102992</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.596817763968827</v>
+        <v>-4.394716197890926</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.008624946201713</v>
+        <v>0.9742253240866638</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2760141058357203</v>
+        <v>-0.2402739761267562</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.68210001260156</v>
+        <v>2.588303841880728</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.853199771933659</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.484440762786154</v>
+        <v>-4.428892883988961</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.05906704250545</v>
+        <v>0.966045945478117</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2760141058357203</v>
+        <v>-0.2402739761267562</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.687591308432227</v>
+        <v>2.593795137711395</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.864696973702198</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.682675331672885</v>
+        <v>-4.627127452875691</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9912704167192965</v>
+        <v>0.8982493196919639</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4742486747224509</v>
+        <v>-0.4385085450134868</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.580147768868728</v>
+        <v>2.486351598147896</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.703052693702851</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.765676612698164</v>
+        <v>-4.71012873390097</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7964256243098382</v>
+        <v>0.7034045272825056</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4928195592496247</v>
+        <v>-0.4570794295406606</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.407360958153077</v>
+        <v>2.313564787432245</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.823202354422057</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.892743619005152</v>
+        <v>-4.837195740207958</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8657484825062487</v>
+        <v>0.7727273854789158</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4928195592496247</v>
+        <v>-0.4570794295406606</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.527510618872282</v>
+        <v>2.43371444815145</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.83771538052438</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.979342201986255</v>
+        <v>-4.923794323189061</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8456220754161303</v>
+        <v>0.7526009783887977</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4928195592496247</v>
+        <v>-0.4570794295406606</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.542023644974605</v>
+        <v>2.448227474253773</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913419</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.835134821866748</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.940958539428104</v>
+        <v>-4.88541066063091</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8583949817817595</v>
+        <v>0.7653738847544269</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4544358966914735</v>
+        <v>-0.4186957669825094</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.562473283851864</v>
+        <v>2.468677113131033</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.83186385071205</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.763842209392938</v>
+        <v>-4.708294330595744</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.925970542641128</v>
+        <v>0.8329494456137951</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4544358966914735</v>
+        <v>-0.4186957669825094</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.559202312697167</v>
+        <v>2.465406141976335</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.832547242473964</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.734140085416644</v>
+        <v>-4.678592206619451</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9385347839935585</v>
+        <v>0.8455136869662256</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4589060219067869</v>
+        <v>-0.4231658921978227</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.557203629329892</v>
+        <v>2.46340745860906</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.826334217780378</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.554764664177877</v>
+        <v>-4.499216785380683</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.00407192779548</v>
+        <v>0.9110508307681471</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3021292637360682</v>
+        <v>-0.2663891340271041</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.645056659538737</v>
+        <v>2.551260488817905</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.807141673111968</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.599778877698483</v>
+        <v>-4.544230998901289</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.966873697718827</v>
+        <v>0.8738526006914942</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3324781590506728</v>
+        <v>-0.2967380293417087</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.607654777681564</v>
+        <v>2.513858606960732</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.812833235450913</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.866783387970918</v>
+        <v>-4.811235509173724</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8657634559487988</v>
+        <v>0.7727423589214659</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5268411970936213</v>
+        <v>-0.4911010673846573</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.496728517194741</v>
+        <v>2.402932346473909</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.812037157347415</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.967981169408091</v>
+        <v>-4.912433290610897</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8244882652704311</v>
+        <v>0.7314671682430984</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5952500106389405</v>
+        <v>-0.5595098809299764</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.454887150964051</v>
+        <v>2.361090980243219</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.809637118901732</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.935505583237319</v>
+        <v>-4.879957704440125</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8350784612930566</v>
+        <v>0.742057364265724</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5952500106389405</v>
+        <v>-0.5595098809299764</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.452487112518368</v>
+        <v>2.358690941797536</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.806161838109976</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.916467455530022</v>
+        <v>-4.860919576732828</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8392184315842206</v>
+        <v>0.7461973345568877</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.653433621970135</v>
+        <v>-0.617693492261171</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.414101664927896</v>
+        <v>2.320305494207064</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.983743707048657</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.94759408668064</v>
+        <v>-4.892046207883446</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.004349648062654</v>
+        <v>0.9113285510353211</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.653433621970135</v>
+        <v>-0.617693492261171</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.591683533866576</v>
+        <v>2.497887363145745</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.984577036034791</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.999914467281432</v>
+        <v>-4.944366588484238</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9842548248084706</v>
+        <v>0.8912337277811377</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6184867619612628</v>
+        <v>-0.5827466322522988</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.613484978858033</v>
+        <v>2.519688808137201</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.990585566431716</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.144237373206351</v>
+        <v>-5.088689494409157</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9325341928354289</v>
+        <v>0.8395130958080963</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6184867619612628</v>
+        <v>-0.5827466322522988</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.619493509254959</v>
+        <v>2.525697338534127</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.069738214223738</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.996494402971348</v>
+        <v>-4.940946524174154</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.070784028721452</v>
+        <v>0.9777629316941192</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4506794047263797</v>
+        <v>-0.4149392750174157</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.799330571387911</v>
+        <v>2.705534400667079</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.072531835755219</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.098509085502569</v>
+        <v>-5.042961206705376</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.032771777240444</v>
+        <v>0.9397506802131117</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4506794047263797</v>
+        <v>-0.4149392750174157</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.802124192919392</v>
+        <v>2.70832802219856</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.073194184146878</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.961899741408477</v>
+        <v>-4.906351862611283</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.08807786326974</v>
+        <v>0.995056766242407</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3140700606322872</v>
+        <v>-0.2783299309233232</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.884752147767506</v>
+        <v>2.790955977046674</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.072274660886988</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.104665074231127</v>
+        <v>-5.049117195433933</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.03005220688079</v>
+        <v>0.9370311098534572</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4568353934549376</v>
+        <v>-0.4210952637459736</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.798173424814026</v>
+        <v>2.704377254093194</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.138610214683809</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.042367075455005</v>
+        <v>-4.986819196657811</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.12130696018806</v>
+        <v>1.028285863160727</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4568353934549376</v>
+        <v>-0.4210952637459736</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.864508978610846</v>
+        <v>2.770712807890015</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.847191087073207</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.840576877789847</v>
+        <v>-4.785028998992653</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9106039116435209</v>
+        <v>0.8175828146161883</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2588172012857832</v>
+        <v>-0.2230770715768192</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.691900766301737</v>
+        <v>2.598104595580905</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.917481319395382</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.780686196147253</v>
+        <v>-4.725138317350059</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.004850416622733</v>
+        <v>0.9118293195954008</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1989265196431897</v>
+        <v>-0.1631863899342257</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.798125407609469</v>
+        <v>2.704329236888637</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.932109055511426</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.878426740772228</v>
+        <v>-4.822878861975034</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9803819348887874</v>
+        <v>0.8873608378614546</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2148157977761699</v>
+        <v>-0.1790756680672059</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.803219576845724</v>
+        <v>2.709423406124892</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.930645036336097</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.054764500895157</v>
+        <v>-4.999216622097963</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9083828116642874</v>
+        <v>0.8153617146369547</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3911535578990993</v>
+        <v>-0.3554134281901353</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.695952901596638</v>
+        <v>2.602156730875806</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.929136654376026</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.054075128733934</v>
+        <v>-4.99852724993674</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9071501785687053</v>
+        <v>0.8141290815413724</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3911535578990993</v>
+        <v>-0.3554134281901353</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.694444519636567</v>
+        <v>2.600648348915735</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.928999521811462</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.060646093788526</v>
+        <v>-5.005098214991333</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9043846599823042</v>
+        <v>0.8113635629549716</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3977245229536923</v>
+        <v>-0.3619843932447283</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.690364808039247</v>
+        <v>2.596568637318415</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.928999521811462</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.052692123493754</v>
+        <v>-4.99714424469656</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9075662481002134</v>
+        <v>0.8145451510728805</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3977245229536923</v>
+        <v>-0.3619843932447283</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.690364808039247</v>
+        <v>2.596568637318415</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.935381278839267</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.042318747160667</v>
+        <v>-4.986770868363473</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9180973556612524</v>
+        <v>0.8250762586339198</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.387351146620605</v>
+        <v>-0.351611016911641</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.702970590866904</v>
+        <v>2.609174420146072</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.940273652213992</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.914634437366371</v>
+        <v>-4.859086558569177</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.974063452953696</v>
+        <v>0.8810423559263632</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2596668368263085</v>
+        <v>-0.2239267071173445</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.784473550118207</v>
+        <v>2.690677379397375</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.927028324689864</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.97530102776876</v>
+        <v>-4.919753148971566</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9365514892686126</v>
+        <v>0.84353039224128</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3413651535448422</v>
+        <v>-0.3056250238358782</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.722209232562959</v>
+        <v>2.628413061842127</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.931126027300492</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.910307167835114</v>
+        <v>-4.85475928903792</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9666467358526996</v>
+        <v>0.8736256388253667</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3145345389406868</v>
+        <v>-0.2787944092317228</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742405303936081</v>
+        <v>2.648609133215249</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674306</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.93528696693157</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.011065803592112</v>
+        <v>-4.955517924794918</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9305042211809784</v>
+        <v>0.8374831241536456</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4033601076676923</v>
+        <v>-0.3676199779587283</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.693270902330955</v>
+        <v>2.599474731610123</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.748975463424548</v>
+        <v>3.448975079884211</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.778926119002515</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.011065803592112</v>
+        <v>-4.822771518422014</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9305042211809784</v>
+        <v>0.8964612892306443</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4033601076676923</v>
+        <v>-0.2348735715858237</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.771989915988883</v>
+        <v>2.685002177961703</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240602.xlsx
+++ b/tame_output/ON/bt/strategyON_20240602.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-22.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-674.8%</t>
+          <t>-661.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.4%</t>
+          <t>457.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.8%</t>
+          <t>-629.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-270.3%</t>
+          <t>-265.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.6%</t>
+          <t>-274.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-302.0%</t>
+          <t>-289.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-126.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.5%</t>
+          <t>-250.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-181.6%</t>
+          <t>-173.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.5%</t>
+          <t>-172.6%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.234492220664831</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.62292713737135</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8573291850165997</v>
+        <v>0.9879402307852079</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.631477960960989</v>
+        <v>3.709844588422154</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.568392735755242</v>
+        <v>-1.437781689986634</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.489233147934107</v>
+        <v>2.541477566241551</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8954085957821715</v>
+        <v>1.02601964155078</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.654191824019255</v>
+        <v>3.732558451480419</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.776396794108319</v>
+        <v>-1.645785748339711</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.410923669146801</v>
+        <v>2.463168087454245</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8954085957821715</v>
+        <v>1.02601964155078</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.65908396857318</v>
+        <v>3.737450596034344</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.987809214996294</v>
+        <v>-1.857198169227686</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.3214401571296</v>
+        <v>2.373684575437043</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6839961748941964</v>
+        <v>0.8146072206628046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.527317972378383</v>
+        <v>3.605684599839547</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.326967592584817</v>
+        <v>-2.196356546816208</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.17886110540064</v>
+        <v>2.231105523708083</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3448377973056743</v>
+        <v>0.4754488430742825</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.316907245131719</v>
+        <v>3.395273872592883</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.535458374036501</v>
+        <v>-2.404847328267893</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.115803082558734</v>
+        <v>2.168047500866177</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1363470158539899</v>
+        <v>0.2669580616225981</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.212151065999476</v>
+        <v>3.290517693460641</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.782659558801723</v>
+        <v>-2.652048513033114</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.025021359061214</v>
+        <v>2.077265777368657</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1565003693528023</v>
+        <v>0.2871114151214105</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.232341828507332</v>
+        <v>3.310708455968497</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.27504458682582</v>
+        <v>-3.144433541057211</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.829173739895307</v>
+        <v>1.881418158202751</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3358846586712944</v>
+        <v>-0.2052736129026863</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.938017203736606</v>
+        <v>3.016383831197771</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.660224977755892</v>
+        <v>-3.529613931987284</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.673644122336142</v>
+        <v>1.725888540643585</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3358846586712944</v>
+        <v>-0.2052736129026863</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.936559742549469</v>
+        <v>3.014926370010635</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.003907750982555</v>
+        <v>-3.873296705213947</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537940136500093</v>
+        <v>1.590184554807536</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4437907106985126</v>
+        <v>-0.3131796649299045</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.873585234787755</v>
+        <v>2.95195186224892</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.210419527869576</v>
+        <v>-4.079808482100968</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.451441484401542</v>
+        <v>1.503685902708986</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6503024875855341</v>
+        <v>-0.5196914418169259</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.7457842273118</v>
+        <v>2.824150854772965</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.466260613648269</v>
+        <v>-4.335649567879661</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.350877976790325</v>
+        <v>1.403122395097768</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6503024875855341</v>
+        <v>-0.5196914418169259</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.747557154012059</v>
+        <v>2.825923781473224</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.898066406798057</v>
+        <v>-4.767455361029448</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.164488546997814</v>
+        <v>1.216732965305257</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7867199840268011</v>
+        <v>-0.6561089382581929</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.652039543614704</v>
+        <v>2.730406171075868</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.132760400930609</v>
+        <v>-5.002149355162</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.058895724346884</v>
+        <v>1.111140142654327</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7803837167975459</v>
+        <v>-0.6497726710289378</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.644126078954347</v>
+        <v>2.722492706415512</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.468423048161061</v>
+        <v>-5.337812002392453</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9232112571106676</v>
+        <v>0.9754556754181114</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7803837167975459</v>
+        <v>-0.6497726710289378</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.642706670610313</v>
+        <v>2.721073298071477</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.832049293061375</v>
+        <v>-5.701438247292766</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7842483193847842</v>
+        <v>0.8364927376922275</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8786053536646717</v>
+        <v>-0.7479943078960636</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.590261248724278</v>
+        <v>2.668627876185443</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.197176675700121</v>
+        <v>-6.066565629931513</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6374518813351169</v>
+        <v>0.6896962996425602</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.174916137963684</v>
+        <v>-1.044305092195076</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.411729293150702</v>
+        <v>2.490095920611867</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.605765452880799</v>
+        <v>-6.475154407112191</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4727779144776045</v>
+        <v>0.5250223327850478</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.165337570857054</v>
+        <v>2.243704198318219</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.882341553196632</v>
+        <v>-6.751730507428023</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.357332906822732</v>
+        <v>0.4095773251301758</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.160523003328515</v>
+        <v>2.23888963078968</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.298733427483629</v>
+        <v>-7.168122381715021</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1887702077168107</v>
+        <v>0.2410146260242541</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.158517053937392</v>
+        <v>2.236883681398557</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.615345370024277</v>
+        <v>-7.484734324255669</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07238412136923023</v>
+        <v>0.1246285396766735</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.168775744606071</v>
+        <v>2.247142372067236</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.961220192009087</v>
+        <v>-7.830609146240478</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0698662422789984</v>
+        <v>-0.01762182397155465</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.164875309751767</v>
+        <v>2.243241937212932</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.124800070193471</v>
+        <v>-7.994189024424863</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1368932734977508</v>
+        <v>-0.08464885519030751</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.583504915144363</v>
+        <v>-1.452893869375754</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.163280229806768</v>
+        <v>2.241646857267932</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.421461412003669</v>
+        <v>-8.290850366235061</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2517788342926219</v>
+        <v>-0.1995344159851786</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.521637005109633</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.125813324295649</v>
+        <v>2.204179951756814</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.626492592777986</v>
+        <v>-8.495881547009377</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3378176111367517</v>
+        <v>-0.2855731928293084</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.521637005109633</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.121787019761245</v>
+        <v>2.20015364722241</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.009493981520617</v>
+        <v>-8.878882935752008</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4911202679553881</v>
+        <v>-0.4388758496479448</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.652248050878241</v>
+        <v>-1.521637005109633</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.121684918439661</v>
+        <v>2.200051545900826</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.191363772505651</v>
+        <v>-9.060752726737043</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5612966683779721</v>
+        <v>-0.5090522500705288</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.834117841863276</v>
+        <v>-1.703506796094668</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.01513455982007</v>
+        <v>2.093501187281235</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.550894095009653</v>
+        <v>-9.420283049241045</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6997584940815225</v>
+        <v>-0.6475140757740792</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.834117841863276</v>
+        <v>-1.703506796094668</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.020484863118121</v>
+        <v>2.098851490579285</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.601243158463875</v>
+        <v>-9.470632112695267</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.711982099506034</v>
+        <v>-0.6597376811985902</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.884466905317498</v>
+        <v>-1.75385585954889</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.998191445002765</v>
+        <v>2.07655807246393</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.698862435885271</v>
+        <v>-9.568251390116663</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7479880598528235</v>
+        <v>-0.6957436415453802</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.982086182738895</v>
+        <v>-1.851475136970287</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.942661629171695</v>
+        <v>2.021028256632861</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.846388523890914</v>
+        <v>-9.715777478122305</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8041049387335084</v>
+        <v>-0.7518605204260651</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.129612270744539</v>
+        <v>-1.99900122497593</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.857039532689882</v>
+        <v>1.935406160151047</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.05064669922078</v>
+        <v>-9.920035653452169</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8802950117468118</v>
+        <v>-0.828050593439368</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.257251215358528</v>
+        <v>-2.126640169589919</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.785969363040131</v>
+        <v>1.864335990501296</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.19245647342757</v>
+        <v>-10.06184542765896</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9325363669450906</v>
+        <v>-0.8802919486376468</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.428530013004103</v>
+        <v>-2.297918967235494</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.687684638937222</v>
+        <v>1.766051266398387</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.11898664176012</v>
+        <v>-9.988375595991508</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8877767327846895</v>
+        <v>-0.8355323144772466</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.355060181336655</v>
+        <v>-2.224449135568046</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.747138239431112</v>
+        <v>1.825504866892277</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.29411105914666</v>
+        <v>-10.16350001337805</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9432712789917908</v>
+        <v>-0.891026860684347</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.530184598723198</v>
+        <v>-2.39957355295459</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.656618809746702</v>
+        <v>1.734985437207867</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.52856315316115</v>
+        <v>-10.39795210739254</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.044271281499182</v>
+        <v>-0.9920268631917391</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.530184598723198</v>
+        <v>-2.39957355295459</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.649399644845106</v>
+        <v>1.727766272306271</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.81636699769839</v>
+        <v>-10.68575595192978</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.166065010088054</v>
+        <v>-1.11382059178061</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.817988443260437</v>
+        <v>-2.687377397491828</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.470045147348787</v>
+        <v>1.548411774809952</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.86915315329871</v>
+        <v>-10.73854210753011</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.186063682489628</v>
+        <v>-1.133819264182184</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.913663929842834</v>
+        <v>-2.783052884074225</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.413755645237905</v>
+        <v>1.49212227269907</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.995189946667</v>
+        <v>-10.8645789008984</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.233784671207829</v>
+        <v>-1.181540252900386</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.757801261264483</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.431600347552865</v>
+        <v>1.509966975014031</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.94317443269819</v>
+        <v>-10.81256338692958</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.208988129933903</v>
+        <v>-1.15674371162646</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.757801261264483</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.435590683239266</v>
+        <v>1.513957310700431</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.08484627442231</v>
+        <v>-10.9542352286537</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.267132093522293</v>
+        <v>-1.214887675214849</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.888412307033091</v>
+        <v>-2.757801261264483</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.434115456340525</v>
+        <v>1.51248208380169</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.03525542999748</v>
+        <v>-10.90464438422887</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.232242345587487</v>
+        <v>-1.179997927280044</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.838821462608257</v>
+        <v>-2.708210416839649</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.478923373160297</v>
+        <v>1.557290000621462</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.83610332276038</v>
+        <v>-10.70549227699177</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.165632636339331</v>
+        <v>-1.113388218031887</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.673498936658444</v>
+        <v>-2.542887890889836</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.565065755083502</v>
+        <v>1.643432382544667</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.61025817004097</v>
+        <v>-10.47964712427236</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.065715502215358</v>
+        <v>-1.013471083907914</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.63157226107128</v>
+        <v>-2.500961215302672</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.599800833472009</v>
+        <v>1.678167460933174</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.48567951370338</v>
+        <v>-10.35506846793477</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.014744895124262</v>
+        <v>-0.9625004768168179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.63157226107128</v>
+        <v>-2.500961215302672</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.600939978028068</v>
+        <v>1.679306605489233</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.53857480174766</v>
+        <v>-10.40796375597905</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.033269236179869</v>
+        <v>-0.9810248178724246</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.626616914982834</v>
+        <v>-2.496005869214226</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.606546959843243</v>
+        <v>1.684913587304408</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25466607081891</v>
+        <v>-10.1240550250503</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9139720395697326</v>
+        <v>-0.8617276212622889</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.626616914982834</v>
+        <v>-2.496005869214226</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.61228066408188</v>
+        <v>1.690647291543045</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18329967820927</v>
+        <v>-10.05268863244066</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8951627449197392</v>
+        <v>-0.8429183266122955</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.424639476604578</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.645363237253803</v>
+        <v>1.723729864714968</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.919462811005197</v>
+        <v>-9.788851765236586</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7995114793510187</v>
+        <v>-0.747267061043575</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.424639476604578</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.635479755940896</v>
+        <v>1.713846383402061</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.652221010136799</v>
+        <v>-9.521609964368189</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6944493195030335</v>
+        <v>-0.6422049011955893</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.555250522373186</v>
+        <v>-2.424639476604578</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.633645195441522</v>
+        <v>1.712011822902687</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.554313971460308</v>
+        <v>-9.423702925691698</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6555868190058982</v>
+        <v>-0.603342400698454</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.48726477251263</v>
+        <v>-2.356653726744021</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.674136330384395</v>
+        <v>1.75250295784556</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.53036043048435</v>
+        <v>-9.39974938471574</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6453368964700212</v>
+        <v>-0.593092478162577</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.463311231536672</v>
+        <v>-2.332700185768064</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.689176961115463</v>
+        <v>1.767543588576628</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.266300492161553</v>
+        <v>-9.135689446392943</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5529732373026546</v>
+        <v>-0.5007288189952108</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.199251293213876</v>
+        <v>-2.068640247445268</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.834352607947389</v>
+        <v>1.912719235408554</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.559220868656716</v>
+        <v>-8.428609822888106</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2729284215610206</v>
+        <v>-0.2206840032535764</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.199251293213876</v>
+        <v>-2.068640247445268</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.831565574287088</v>
+        <v>1.909932201748253</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.519036570290526</v>
+        <v>-8.388425524521915</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2565110783267031</v>
+        <v>-0.2042666600192589</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.159066994847685</v>
+        <v>-2.028455949079077</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.856019777194644</v>
+        <v>1.934386404655809</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.438966774752721</v>
+        <v>-8.308355728984111</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2251163388908246</v>
+        <v>-0.1728719205833804</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.078997199309881</v>
+        <v>-1.948386153541273</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.903428475738083</v>
+        <v>1.981795103199248</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.205485552523122</v>
+        <v>-8.074874506754512</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1237994211611322</v>
+        <v>-0.07155500285368799</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.845515977080283</v>
+        <v>-1.714904931311674</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.051441637913695</v>
+        <v>2.12980826537486</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.055819161515608</v>
+        <v>-7.925208115746996</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.06682507507108593</v>
+        <v>-0.01458065676364129</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.752612485837747</v>
+        <v>-1.622001440069138</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.104291522346257</v>
+        <v>2.182658149807422</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.923543687884721</v>
+        <v>-7.79293264211611</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.01854739887170398</v>
+        <v>0.03369701943574022</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.62033701220686</v>
+        <v>-1.489725966438252</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.179024293271816</v>
+        <v>2.257390920732981</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.732944013211569</v>
+        <v>-7.602332967442957</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06050753168519352</v>
+        <v>0.1127519499926382</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.429737337533707</v>
+        <v>-1.299126291765099</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.296199158763344</v>
+        <v>2.37456578622451</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.483944214527988</v>
+        <v>-7.353333168759376</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1730137923822848</v>
+        <v>0.2252582106897294</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.429737337533707</v>
+        <v>-1.299126291765099</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.309105499987003</v>
+        <v>2.387472127448168</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.589534204301092</v>
+        <v>-7.458923158532481</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.00280186687382411</v>
+        <v>0.05504628518126875</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.535327327306812</v>
+        <v>-1.404716281538203</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.117775576523922</v>
+        <v>2.196142203985087</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.608269106419689</v>
+        <v>-7.477658060651078</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04385224790347175</v>
+        <v>0.09609666621091639</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.535327327306812</v>
+        <v>-1.404716281538203</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.166319918401008</v>
+        <v>2.244686545862173</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.46032906501209</v>
+        <v>-7.329718019243479</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0168506582216561</v>
+        <v>0.03539376008578854</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.515006411398254</v>
+        <v>-1.384395365629645</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.058633545257975</v>
+        <v>2.13700017271914</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.443170914880795</v>
+        <v>-7.312559869112184</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01870138442261648</v>
+        <v>0.03354303388482816</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.367237215498351</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.060214449083273</v>
+        <v>2.138581076544439</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.399622508110105</v>
+        <v>-7.269011462341494</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.008242633809433464</v>
+        <v>0.04400178449801118</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.367237215498351</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.05325383698818</v>
+        <v>2.131620464449345</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.157474114656247</v>
+        <v>-7.026863068887636</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1030790779532529</v>
+        <v>0.1553234962606975</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.367237215498351</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.067716191369323</v>
+        <v>2.146082818830489</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.049214977533725</v>
+        <v>-6.918603931765114</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1409148532614566</v>
+        <v>0.1931592715689012</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.49784826126696</v>
+        <v>-1.367237215498351</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.062248311828518</v>
+        <v>2.140614939289684</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.925923842716594</v>
+        <v>-6.795312796947983</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1877294011988857</v>
+        <v>0.2399738195063303</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.374557126449829</v>
+        <v>-1.243946080681221</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.133721086729374</v>
+        <v>2.212087714190539</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.904774643813151</v>
+        <v>-6.77416359804454</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2038900589975885</v>
+        <v>0.2561344773050327</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.353407927546386</v>
+        <v>-1.222796881777777</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.154111584308765</v>
+        <v>2.23247821176993</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.661009201829707</v>
+        <v>-6.530398156061096</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2971769441380165</v>
+        <v>0.3494213624454612</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.353407927546386</v>
+        <v>-1.222796881777777</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.149892292655815</v>
+        <v>2.228258920116981</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.514112174111837</v>
+        <v>-6.424420493992401</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3580600691451807</v>
+        <v>0.3939367411929551</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.210037097500694</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.180611551762984</v>
+        <v>2.238039104603247</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.264261780162762</v>
+        <v>-6.174570100043327</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4507423017085128</v>
+        <v>0.4866189737562867</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.210037097500694</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.173353626746687</v>
+        <v>2.230781179586949</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.08836968769533</v>
+        <v>-5.998678007575894</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.524698262216134</v>
+        <v>0.5605749342639088</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.305749685567798</v>
+        <v>-1.210037097500694</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.176952750267335</v>
+        <v>2.234380303107598</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.916923224672867</v>
+        <v>-5.82723154455343</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6066043534796735</v>
+        <v>0.6424810255274478</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.134303222545335</v>
+        <v>-1.038590634478231</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.293148134135367</v>
+        <v>2.350575686975629</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.691890225004044</v>
+        <v>-5.602198544884607</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6956380309634995</v>
+        <v>0.7315147030112743</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9092702228765118</v>
+        <v>-0.8135576348094077</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.427188411552958</v>
+        <v>2.48461596439322</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.628254482770109</v>
+        <v>-5.538562802650673</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7257871289113904</v>
+        <v>0.7616638009591652</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8456344806425773</v>
+        <v>-0.7499218925754731</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.470064657947636</v>
+        <v>2.527492210787898</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.535254441564211</v>
+        <v>-5.445562761444775</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7441814041775454</v>
+        <v>0.7800580762253202</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8456344806425773</v>
+        <v>-0.7499218925754731</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.451258916731431</v>
+        <v>2.508686469571694</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.294823944759351</v>
+        <v>-5.205132264639914</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8420966795243672</v>
+        <v>0.8779733515721415</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.605203983837717</v>
+        <v>-0.5094913957706129</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.597260291439225</v>
+        <v>2.654687844279487</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.222581376588156</v>
+        <v>-5.13288969646872</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8749230206276652</v>
+        <v>0.9107996926754396</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.605203983837717</v>
+        <v>-0.5094913957706129</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.601189605274045</v>
+        <v>2.658617158114307</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169583054306768</v>
+        <v>-5.079891374187332</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8968009334575604</v>
+        <v>0.9326776055053347</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5498677248357782</v>
+        <v>-0.454155136768674</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.635069944592548</v>
+        <v>2.692497497432811</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.060778168827041</v>
+        <v>-4.971086488707605</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9373209588694444</v>
+        <v>0.9731976309172192</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5498677248357782</v>
+        <v>-0.454155136768674</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.632068015812542</v>
+        <v>2.689495568652804</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.840757370790031</v>
+        <v>-4.751065690670594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.026908315094863</v>
+        <v>1.062784987142638</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4086478797677979</v>
+        <v>-0.3129352917006938</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.718378959863944</v>
+        <v>2.775806512704206</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.707889681726753</v>
+        <v>-4.618198001607317</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.095949573521997</v>
+        <v>1.131826245569772</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4086478797677979</v>
+        <v>-0.3129352917006938</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.734273142665767</v>
+        <v>2.79170069550603</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.548374578207383</v>
+        <v>-4.458682898087947</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.160901459370047</v>
+        <v>1.196778131417822</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.249132776248428</v>
+        <v>-0.1534201881813239</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.831128049217691</v>
+        <v>2.888555602057953</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.403702433107646</v>
+        <v>-4.314010752988209</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.228858419971382</v>
+        <v>1.264735092019156</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1044606311486906</v>
+        <v>-0.008748043081586443</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.928019438838974</v>
+        <v>2.985446991679236</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.463577260465338</v>
+        <v>-4.373885580345902</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.190945980429731</v>
+        <v>1.226822652477505</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1643354585063827</v>
+        <v>-0.06862287043927856</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.878132033825784</v>
+        <v>2.935559586666046</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.376777762686329</v>
+        <v>-4.287086082566892</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.2480662728639</v>
+        <v>1.283942944911675</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1643354585063827</v>
+        <v>-0.06862287043927856</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.90053252714835</v>
+        <v>2.957960079988613</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.379247469148135</v>
+        <v>-4.289555789028698</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.24715079165259</v>
+        <v>1.283027463700365</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1668051649681889</v>
+        <v>-0.07109257690108473</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.899123104644679</v>
+        <v>2.956550657484941</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.447617655472145</v>
+        <v>-4.357925975352709</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.230809639597688</v>
+        <v>1.266686311645463</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.06181687786486978</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.915695446541109</v>
+        <v>2.973122999381372</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.556155836388279</v>
+        <v>-4.466464156268843</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177831075863126</v>
+        <v>1.213707747910901</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.06181687786486978</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.906132155173001</v>
+        <v>2.963559708013263</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.587148995716984</v>
+        <v>-4.497457315597548</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9901433771720307</v>
+        <v>1.026020049219805</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.06181687786486978</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.730841720213387</v>
+        <v>2.78826927305365</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.411674735924516</v>
+        <v>-4.321983055805079</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064900313080806</v>
+        <v>1.10077698512858</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.06181687786486978</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.735408952205175</v>
+        <v>2.792836505045438</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.522610988565765</v>
+        <v>-4.432919308446328</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9962678407855134</v>
+        <v>1.032144512833288</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1575294659319739</v>
+        <v>-0.06181687786486978</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.711150980966382</v>
+        <v>2.768578533806645</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.725637566108998</v>
+        <v>-4.635945885989561</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9181885949881257</v>
+        <v>0.9540652670359002</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.2648434554081032</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.592466419660348</v>
+        <v>2.64989397250061</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226416</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.567711967173705</v>
+        <v>-4.478020287054268</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9915312209943752</v>
+        <v>1.02740789304215</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.2648434554081032</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.60263880609248</v>
+        <v>2.660066358932743</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.481468504147327</v>
+        <v>-4.39177682402789</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.020974876778787</v>
+        <v>1.056851548826561</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3605560434752073</v>
+        <v>-0.2648434554081032</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.59758507666634</v>
+        <v>2.655012629506603</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.526775323546307</v>
+        <v>-4.43708364342687</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9946279244637202</v>
+        <v>1.030504596511495</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4013662064844381</v>
+        <v>-0.305653618417334</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.564874754305328</v>
+        <v>2.62230230714559</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.555808428248608</v>
+        <v>-4.466116748129171</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9835665556159014</v>
+        <v>1.019443227663676</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4013662064844381</v>
+        <v>-0.305653618417334</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.565426627338429</v>
+        <v>2.622854180178692</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.462997946797748</v>
+        <v>-4.373306266678312</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9499634400876109</v>
+        <v>0.9858401121353855</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3085557250335788</v>
+        <v>-0.2128431369664746</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.55038560810031</v>
+        <v>2.607813160940573</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.507387416127176</v>
+        <v>-4.417695736007739</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9340811282804407</v>
+        <v>0.9699578003282152</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3529451943630064</v>
+        <v>-0.2572326062959023</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.525625402427255</v>
+        <v>2.583052955267517</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.394716197890926</v>
+        <v>-4.305024517771489</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9742253240866638</v>
+        <v>1.010101996134438</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2402739761267562</v>
+        <v>-0.1445613880596521</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.588303841880728</v>
+        <v>2.64573139472099</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.428892883988961</v>
+        <v>-4.339201203869524</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.966045945478117</v>
+        <v>1.001922617525892</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2402739761267562</v>
+        <v>-0.1445613880596521</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.593795137711395</v>
+        <v>2.651222690551657</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.627127452875691</v>
+        <v>-4.537435772756255</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8982493196919639</v>
+        <v>0.9341259917397384</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4385085450134868</v>
+        <v>-0.3427959569463827</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.486351598147896</v>
+        <v>2.543779150988158</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.71012873390097</v>
+        <v>-4.620437053781534</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7034045272825056</v>
+        <v>0.7392811993302801</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.3613668414735564</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.313564787432245</v>
+        <v>2.370992340272507</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.837195740207958</v>
+        <v>-4.747504060088522</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7727273854789158</v>
+        <v>0.8086040575266904</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.3613668414735564</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.43371444815145</v>
+        <v>2.491142000991713</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.923794323189061</v>
+        <v>-4.834102643069625</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7526009783887977</v>
+        <v>0.7884776504365723</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4570794295406606</v>
+        <v>-0.3613668414735564</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.448227474253773</v>
+        <v>2.505655027094036</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913419</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.88541066063091</v>
+        <v>-4.795718980511474</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7653738847544269</v>
+        <v>0.8012505568022015</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4186957669825094</v>
+        <v>-0.3229831789154052</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.468677113131033</v>
+        <v>2.526104665971295</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.708294330595744</v>
+        <v>-4.618602650476308</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8329494456137951</v>
+        <v>0.8688261176615697</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4186957669825094</v>
+        <v>-0.3229831789154052</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.465406141976335</v>
+        <v>2.522833694816597</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793896</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.678592206619451</v>
+        <v>-4.588900526500014</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8455136869662256</v>
+        <v>0.8813903590140004</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4231658921978227</v>
+        <v>-0.3274533041307186</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.46340745860906</v>
+        <v>2.520835011449322</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.499216785380683</v>
+        <v>-4.409525105261246</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9110508307681471</v>
+        <v>0.9469275028159219</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2663891340271041</v>
+        <v>-0.1706765459599999</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.551260488817905</v>
+        <v>2.608688041658168</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.544230998901289</v>
+        <v>-4.454539318781853</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8738526006914942</v>
+        <v>0.909729272739269</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2967380293417087</v>
+        <v>-0.2010254412746045</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.513858606960732</v>
+        <v>2.571286159800995</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.811235509173724</v>
+        <v>-4.721543829054288</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7727423589214659</v>
+        <v>0.8086190309692407</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4911010673846573</v>
+        <v>-0.3953884793175531</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.402932346473909</v>
+        <v>2.460359899314172</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.912433290610897</v>
+        <v>-4.822741610491461</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7314671682430984</v>
+        <v>0.767343840290873</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5595098809299764</v>
+        <v>-0.4637972928628723</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.361090980243219</v>
+        <v>2.418518533083482</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.879957704440125</v>
+        <v>-4.790266024320688</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.742057364265724</v>
+        <v>0.7779340363134986</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5595098809299764</v>
+        <v>-0.4637972928628723</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.358690941797536</v>
+        <v>2.416118494637798</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.860919576732828</v>
+        <v>-4.771227896613391</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7461973345568877</v>
+        <v>0.7820740066046623</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.617693492261171</v>
+        <v>-0.5219809041940668</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.320305494207064</v>
+        <v>2.377733047047326</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.892046207883446</v>
+        <v>-4.80235452776401</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9113285510353211</v>
+        <v>0.9472052230830956</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.617693492261171</v>
+        <v>-0.5219809041940668</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.497887363145745</v>
+        <v>2.555314915986007</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.944366588484238</v>
+        <v>-4.854674908364801</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8912337277811377</v>
+        <v>0.9271103998289125</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5827466322522988</v>
+        <v>-0.4870340441851947</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.519688808137201</v>
+        <v>2.577116360977464</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.088689494409157</v>
+        <v>-4.99899781428972</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8395130958080963</v>
+        <v>0.8753897678558709</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5827466322522988</v>
+        <v>-0.4870340441851947</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.525697338534127</v>
+        <v>2.58312489137439</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.940946524174154</v>
+        <v>-4.851254844054718</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9777629316941192</v>
+        <v>1.013639603741894</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4149392750174157</v>
+        <v>-0.3192266869503115</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.705534400667079</v>
+        <v>2.762961953507341</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.042961206705376</v>
+        <v>-4.953269526585939</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9397506802131117</v>
+        <v>0.9756273522608863</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4149392750174157</v>
+        <v>-0.3192266869503115</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.70832802219856</v>
+        <v>2.765755575038822</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.906351862611283</v>
+        <v>-4.816660182491846</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.995056766242407</v>
+        <v>1.030933438290182</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2783299309233232</v>
+        <v>-0.1826173428562191</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.790955977046674</v>
+        <v>2.848383529886936</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.049117195433933</v>
+        <v>-4.959425515314496</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9370311098534572</v>
+        <v>0.9729077819012319</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4210952637459736</v>
+        <v>-0.3253826756788695</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.704377254093194</v>
+        <v>2.761804806933456</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.986819196657811</v>
+        <v>-4.897127516538374</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.028285863160727</v>
+        <v>1.064162535208502</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4210952637459736</v>
+        <v>-0.3253826756788695</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.770712807890015</v>
+        <v>2.828140360730277</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.785028998992653</v>
+        <v>-4.695337318873216</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8175828146161883</v>
+        <v>0.8534594866639629</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2230770715768192</v>
+        <v>-0.1273644835097151</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.598104595580905</v>
+        <v>2.655532148421168</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.725138317350059</v>
+        <v>-4.635446637230623</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9118293195954008</v>
+        <v>0.9477059916431754</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1631863899342257</v>
+        <v>-0.0674738018671216</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.704329236888637</v>
+        <v>2.761756789728899</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.822878861975034</v>
+        <v>-4.733187181855597</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8873608378614546</v>
+        <v>0.9232375099092294</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1790756680672059</v>
+        <v>-0.08336308000010179</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.709423406124892</v>
+        <v>2.766850958965155</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.999216622097963</v>
+        <v>-4.909524941978527</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8153617146369547</v>
+        <v>0.8512383866847293</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3554134281901353</v>
+        <v>-0.2597008401230312</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.602156730875806</v>
+        <v>2.659584283716069</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.99852724993674</v>
+        <v>-4.908835569817303</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8141290815413724</v>
+        <v>0.850005753589147</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3554134281901353</v>
+        <v>-0.2597008401230312</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.600648348915735</v>
+        <v>2.658075901755997</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024957</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.005098214991333</v>
+        <v>-4.915406534871896</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8113635629549716</v>
+        <v>0.8472402350027461</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3619843932447283</v>
+        <v>-0.2662718051776241</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.596568637318415</v>
+        <v>2.653996190158677</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.99714424469656</v>
+        <v>-4.907452564577124</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8145451510728805</v>
+        <v>0.8504218231206551</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3619843932447283</v>
+        <v>-0.2662718051776241</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.596568637318415</v>
+        <v>2.653996190158677</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.986770868363473</v>
+        <v>-4.897079188244037</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8250762586339198</v>
+        <v>0.8609529306816945</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.351611016911641</v>
+        <v>-0.2558984288445368</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.609174420146072</v>
+        <v>2.666601972986335</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.859086558569177</v>
+        <v>-4.769394878449741</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8810423559263632</v>
+        <v>0.9169190279741377</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2239267071173445</v>
+        <v>-0.1282141190502404</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.690677379397375</v>
+        <v>2.748104932237637</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.919753148971566</v>
+        <v>-4.830061468852129</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.84353039224128</v>
+        <v>0.8794070642890546</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3056250238358782</v>
+        <v>-0.2099124357687741</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.628413061842127</v>
+        <v>2.685840614682389</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.85475928903792</v>
+        <v>-4.765067608918484</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8736256388253667</v>
+        <v>0.9095023108731413</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2787944092317228</v>
+        <v>-0.1830818211646187</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.648609133215249</v>
+        <v>2.706036686055511</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674306</v>
+        <v>3.817961388674308</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.955517924794918</v>
+        <v>-4.723621301647617</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8374831241536456</v>
+        <v>0.9302417734125661</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3676199779587283</v>
+        <v>-0.3107348077609183</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.599474731610123</v>
+        <v>2.633605833728809</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.448975079884211</v>
+        <v>3.746425362730461</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.893295215423869</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.822771518422014</v>
+        <v>-4.677641987696743</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8964612892306443</v>
+        <v>1.021881996031424</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2348735715858237</v>
+        <v>-0.2647554938100453</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.685002177961703</v>
+        <v>2.734441919137842</v>
       </c>
     </row>
   </sheetData>
